--- a/Experiment Results for Equal Sets with Symmetric Distances v2/Experiment Results Summary for Equal Sets with Symmetric Distances v2.xlsx
+++ b/Experiment Results for Equal Sets with Symmetric Distances v2/Experiment Results Summary for Equal Sets with Symmetric Distances v2.xlsx
@@ -1283,4441 +1283,4441 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1x2x15</t>
+          <t>1x2x40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2x15</t>
+          <t>2x40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1x2x15 : 2x15</t>
+          <t>1x2x40 : 2x40</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>319.741943359375</v>
+        <v>5574.7109375</v>
       </c>
       <c r="F12" t="n">
-        <v>639949</v>
+        <v>1642649</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.90625</v>
+        <v>5.566162109375</v>
       </c>
       <c r="I12" t="n">
-        <v>668113</v>
+        <v>1697285</v>
       </c>
       <c r="J12" t="n">
-        <v>4.4</v>
+        <v>3.33</v>
       </c>
       <c r="K12" t="n">
-        <v>122.519775390625</v>
+        <v>4000.483154296875</v>
       </c>
       <c r="L12" t="n">
-        <v>649925</v>
+        <v>1654333</v>
       </c>
       <c r="M12" t="n">
-        <v>1.56</v>
+        <v>0.71</v>
       </c>
       <c r="N12" t="n">
-        <v>15431.255859375</v>
+        <v>87621.2890625</v>
       </c>
       <c r="O12" t="n">
-        <v>670090</v>
+        <v>1670350</v>
       </c>
       <c r="P12" t="n">
-        <v>4.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.778076171875</v>
+        <v>31.97119140625</v>
       </c>
       <c r="R12" t="n">
-        <v>670090</v>
+        <v>1670350</v>
       </c>
       <c r="S12" t="n">
-        <v>4.71</v>
+        <v>1.69</v>
       </c>
       <c r="T12" t="n">
-        <v>24826.73510742188</v>
+        <v>188483.25390625</v>
       </c>
       <c r="U12" t="n">
-        <v>670090</v>
+        <v>1670350</v>
       </c>
       <c r="V12" t="n">
-        <v>4.71</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1x2x15</t>
+          <t>1x2x40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2x15</t>
+          <t>2x40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1x2x15 : 2x15</t>
+          <t>1x2x40 : 2x40</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>1079.265869140625</v>
+        <v>6092.59619140625</v>
       </c>
       <c r="F13" t="n">
-        <v>631419</v>
+        <v>1636390</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.908935546875</v>
+        <v>5.577880859375</v>
       </c>
       <c r="I13" t="n">
-        <v>658145</v>
+        <v>1686009</v>
       </c>
       <c r="J13" t="n">
-        <v>4.23</v>
+        <v>3.03</v>
       </c>
       <c r="K13" t="n">
-        <v>74.822021484375</v>
+        <v>4461.220947265625</v>
       </c>
       <c r="L13" t="n">
-        <v>639448</v>
+        <v>1648701</v>
       </c>
       <c r="M13" t="n">
-        <v>1.27</v>
+        <v>0.75</v>
       </c>
       <c r="N13" t="n">
-        <v>15450.43579101562</v>
+        <v>88505.75708007812</v>
       </c>
       <c r="O13" t="n">
-        <v>658370</v>
+        <v>1674473</v>
       </c>
       <c r="P13" t="n">
-        <v>4.27</v>
+        <v>2.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.705810546875</v>
+        <v>31.3212890625</v>
       </c>
       <c r="R13" t="n">
-        <v>658370</v>
+        <v>1674473</v>
       </c>
       <c r="S13" t="n">
-        <v>4.27</v>
+        <v>2.33</v>
       </c>
       <c r="T13" t="n">
-        <v>24808.75390625</v>
+        <v>189292.0498046875</v>
       </c>
       <c r="U13" t="n">
-        <v>658370</v>
+        <v>1674473</v>
       </c>
       <c r="V13" t="n">
-        <v>4.27</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1x2x15</t>
+          <t>1x2x40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2x15</t>
+          <t>2x40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1x2x15 : 2x15</t>
+          <t>1x2x40 : 2x40</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>709.0712890625</v>
+        <v>13629.40502929688</v>
       </c>
       <c r="F14" t="n">
-        <v>641082</v>
+        <v>1638987</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.90234375</v>
+        <v>8.239990234375</v>
       </c>
       <c r="I14" t="n">
-        <v>672870</v>
+        <v>1689494</v>
       </c>
       <c r="J14" t="n">
-        <v>4.96</v>
+        <v>3.08</v>
       </c>
       <c r="K14" t="n">
-        <v>99.365234375</v>
+        <v>4638.871337890625</v>
       </c>
       <c r="L14" t="n">
-        <v>648058</v>
+        <v>1653066</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>0.86</v>
       </c>
       <c r="N14" t="n">
-        <v>15532.07666015625</v>
+        <v>87591.72998046875</v>
       </c>
       <c r="O14" t="n">
-        <v>668949</v>
+        <v>1683312</v>
       </c>
       <c r="P14" t="n">
-        <v>4.35</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.762939453125</v>
+        <v>30.9189453125</v>
       </c>
       <c r="R14" t="n">
-        <v>668949</v>
+        <v>1683312</v>
       </c>
       <c r="S14" t="n">
-        <v>4.35</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>24798.31591796875</v>
+        <v>188298.0568847656</v>
       </c>
       <c r="U14" t="n">
-        <v>668949</v>
+        <v>1683312</v>
       </c>
       <c r="V14" t="n">
-        <v>4.35</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1x2x15</t>
+          <t>1x2x40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2x15</t>
+          <t>2x40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1x2x15 : 2x15</t>
+          <t>1x2x40 : 2x40</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>399.50390625</v>
+        <v>8631.515869140625</v>
       </c>
       <c r="F15" t="n">
-        <v>642479</v>
+        <v>1640372</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.980224609375</v>
+        <v>5.27783203125</v>
       </c>
       <c r="I15" t="n">
-        <v>671571</v>
+        <v>1674494</v>
       </c>
       <c r="J15" t="n">
-        <v>4.53</v>
+        <v>2.08</v>
       </c>
       <c r="K15" t="n">
-        <v>87.03173828125</v>
+        <v>3955.9169921875</v>
       </c>
       <c r="L15" t="n">
-        <v>654440</v>
+        <v>1654221</v>
       </c>
       <c r="M15" t="n">
-        <v>1.86</v>
+        <v>0.84</v>
       </c>
       <c r="N15" t="n">
-        <v>15441.89331054688</v>
+        <v>87335.79907226562</v>
       </c>
       <c r="O15" t="n">
-        <v>668259</v>
+        <v>1679469</v>
       </c>
       <c r="P15" t="n">
-        <v>4.01</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.765380859375</v>
+        <v>31.037109375</v>
       </c>
       <c r="R15" t="n">
-        <v>668259</v>
+        <v>1679469</v>
       </c>
       <c r="S15" t="n">
-        <v>4.01</v>
+        <v>2.38</v>
       </c>
       <c r="T15" t="n">
-        <v>24855.16015625</v>
+        <v>189122.9399414062</v>
       </c>
       <c r="U15" t="n">
-        <v>668259</v>
+        <v>1679469</v>
       </c>
       <c r="V15" t="n">
-        <v>4.01</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1x2x15</t>
+          <t>1x2x40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2x15</t>
+          <t>2x40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1x2x15 : 2x15</t>
+          <t>1x2x40 : 2x40</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>403.687744140625</v>
+        <v>9186.319091796877</v>
       </c>
       <c r="F16" t="n">
-        <v>640704</v>
+        <v>1635207</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.929931640625</v>
+        <v>5.526123046875</v>
       </c>
       <c r="I16" t="n">
-        <v>669479</v>
+        <v>1661564</v>
       </c>
       <c r="J16" t="n">
-        <v>4.49</v>
+        <v>1.61</v>
       </c>
       <c r="K16" t="n">
-        <v>166.362548828125</v>
+        <v>3080.1142578125</v>
       </c>
       <c r="L16" t="n">
-        <v>648286</v>
+        <v>1643347</v>
       </c>
       <c r="M16" t="n">
-        <v>1.18</v>
+        <v>0.5</v>
       </c>
       <c r="N16" t="n">
-        <v>15483.830078125</v>
+        <v>87605.31005859375</v>
       </c>
       <c r="O16" t="n">
-        <v>669105</v>
+        <v>1683014</v>
       </c>
       <c r="P16" t="n">
-        <v>4.43</v>
+        <v>2.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.701171875</v>
+        <v>32.071044921875</v>
       </c>
       <c r="R16" t="n">
-        <v>669105</v>
+        <v>1683014</v>
       </c>
       <c r="S16" t="n">
-        <v>4.43</v>
+        <v>2.92</v>
       </c>
       <c r="T16" t="n">
-        <v>24804.92114257812</v>
+        <v>188348.3190917969</v>
       </c>
       <c r="U16" t="n">
-        <v>669105</v>
+        <v>1683014</v>
       </c>
       <c r="V16" t="n">
-        <v>4.43</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1x2x15</t>
+          <t>1x2x40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2x15</t>
+          <t>2x40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1x2x15 : 2x15</t>
+          <t>1x2x40 : 2x40</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>650.97216796875</v>
+        <v>7143.792236328125</v>
       </c>
       <c r="F17" t="n">
-        <v>639093</v>
+        <v>1641792</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.932861328125</v>
+        <v>5.830810546875</v>
       </c>
       <c r="I17" t="n">
-        <v>652383</v>
+        <v>1689894</v>
       </c>
       <c r="J17" t="n">
-        <v>2.08</v>
+        <v>2.93</v>
       </c>
       <c r="K17" t="n">
-        <v>68.56494140625</v>
+        <v>5163.18310546875</v>
       </c>
       <c r="L17" t="n">
-        <v>646189</v>
+        <v>1658954</v>
       </c>
       <c r="M17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>15568.84814453125</v>
+        <v>88700.6162109375</v>
       </c>
       <c r="O17" t="n">
-        <v>652383</v>
+        <v>1696557</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>3.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.81103515625</v>
+        <v>31.506103515625</v>
       </c>
       <c r="R17" t="n">
-        <v>652383</v>
+        <v>1696557</v>
       </c>
       <c r="S17" t="n">
-        <v>2.08</v>
+        <v>3.34</v>
       </c>
       <c r="T17" t="n">
-        <v>24946.951171875</v>
+        <v>188296.1540527344</v>
       </c>
       <c r="U17" t="n">
-        <v>652383</v>
+        <v>1696557</v>
       </c>
       <c r="V17" t="n">
-        <v>2.08</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1x2x15</t>
+          <t>1x2x40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2x15</t>
+          <t>2x40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1x2x15 : 2x15</t>
+          <t>1x2x40 : 2x40</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>327.651123046875</v>
+        <v>8499.356201171875</v>
       </c>
       <c r="F18" t="n">
-        <v>642152</v>
+        <v>1643588</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9140625</v>
+        <v>5.307861328125</v>
       </c>
       <c r="I18" t="n">
-        <v>663737</v>
+        <v>1696490</v>
       </c>
       <c r="J18" t="n">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="K18" t="n">
-        <v>129.13623046875</v>
+        <v>5514.0087890625</v>
       </c>
       <c r="L18" t="n">
-        <v>647996</v>
+        <v>1659622</v>
       </c>
       <c r="M18" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="N18" t="n">
-        <v>15506.2626953125</v>
+        <v>88258.38403320312</v>
       </c>
       <c r="O18" t="n">
-        <v>678045</v>
+        <v>1682750</v>
       </c>
       <c r="P18" t="n">
-        <v>5.59</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.822998046875</v>
+        <v>32.3681640625</v>
       </c>
       <c r="R18" t="n">
-        <v>678045</v>
+        <v>1682750</v>
       </c>
       <c r="S18" t="n">
-        <v>5.59</v>
+        <v>2.38</v>
       </c>
       <c r="T18" t="n">
-        <v>24951.0146484375</v>
+        <v>189729.3400878907</v>
       </c>
       <c r="U18" t="n">
-        <v>678045</v>
+        <v>1682750</v>
       </c>
       <c r="V18" t="n">
-        <v>5.59</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1x2x15</t>
+          <t>1x2x40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2x15</t>
+          <t>2x40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1x2x15 : 2x15</t>
+          <t>1x2x40 : 2x40</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>472.299072265625</v>
+        <v>6068.254150390625</v>
       </c>
       <c r="F19" t="n">
-        <v>639061</v>
+        <v>1645038</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.90380859375</v>
+        <v>5.470458984375</v>
       </c>
       <c r="I19" t="n">
-        <v>674969</v>
+        <v>1692591</v>
       </c>
       <c r="J19" t="n">
-        <v>5.62</v>
+        <v>2.89</v>
       </c>
       <c r="K19" t="n">
-        <v>161.4091796875</v>
+        <v>3825.430908203125</v>
       </c>
       <c r="L19" t="n">
-        <v>646653</v>
+        <v>1660625</v>
       </c>
       <c r="M19" t="n">
-        <v>1.19</v>
+        <v>0.95</v>
       </c>
       <c r="N19" t="n">
-        <v>15604.94311523438</v>
+        <v>89252.046875</v>
       </c>
       <c r="O19" t="n">
-        <v>674969</v>
+        <v>1696471</v>
       </c>
       <c r="P19" t="n">
-        <v>5.62</v>
+        <v>3.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.899169921875</v>
+        <v>33.218017578125</v>
       </c>
       <c r="R19" t="n">
-        <v>674969</v>
+        <v>1696471</v>
       </c>
       <c r="S19" t="n">
-        <v>5.62</v>
+        <v>3.13</v>
       </c>
       <c r="T19" t="n">
-        <v>24852.47509765625</v>
+        <v>189014.37109375</v>
       </c>
       <c r="U19" t="n">
-        <v>674969</v>
+        <v>1696471</v>
       </c>
       <c r="V19" t="n">
-        <v>5.62</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1x2x15</t>
+          <t>1x2x40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2x15</t>
+          <t>2x40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1x2x15 : 2x15</t>
+          <t>1x2x40 : 2x40</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>398.55615234375</v>
+        <v>12428.09716796875</v>
       </c>
       <c r="F20" t="n">
-        <v>632255</v>
+        <v>1635024</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.930908203125</v>
+        <v>5.35400390625</v>
       </c>
       <c r="I20" t="n">
-        <v>670269</v>
+        <v>1696541</v>
       </c>
       <c r="J20" t="n">
-        <v>6.01</v>
+        <v>3.76</v>
       </c>
       <c r="K20" t="n">
-        <v>199.89306640625</v>
+        <v>5831.58984375</v>
       </c>
       <c r="L20" t="n">
-        <v>635039</v>
+        <v>1646091</v>
       </c>
       <c r="M20" t="n">
-        <v>0.44</v>
+        <v>0.68</v>
       </c>
       <c r="N20" t="n">
-        <v>15590.544921875</v>
+        <v>87708.46875</v>
       </c>
       <c r="O20" t="n">
-        <v>651592</v>
+        <v>1688735</v>
       </c>
       <c r="P20" t="n">
-        <v>3.06</v>
+        <v>3.29</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.841064453125</v>
+        <v>31.553955078125</v>
       </c>
       <c r="R20" t="n">
-        <v>651592</v>
+        <v>1688735</v>
       </c>
       <c r="S20" t="n">
-        <v>3.06</v>
+        <v>3.29</v>
       </c>
       <c r="T20" t="n">
-        <v>24958.20288085937</v>
+        <v>190052.4282226562</v>
       </c>
       <c r="U20" t="n">
-        <v>651592</v>
+        <v>1688735</v>
       </c>
       <c r="V20" t="n">
-        <v>3.06</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1x2x15</t>
+          <t>1x2x40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2x15</t>
+          <t>2x40</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1x2x15 : 2x15</t>
+          <t>1x2x40 : 2x40</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>328.806884765625</v>
+        <v>6512.43115234375</v>
       </c>
       <c r="F21" t="n">
-        <v>642737</v>
+        <v>1634692</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9130859375</v>
+        <v>5.5302734375</v>
       </c>
       <c r="I21" t="n">
-        <v>674436</v>
+        <v>1665723</v>
       </c>
       <c r="J21" t="n">
-        <v>4.93</v>
+        <v>1.9</v>
       </c>
       <c r="K21" t="n">
-        <v>85.758056640625</v>
+        <v>3118.93896484375</v>
       </c>
       <c r="L21" t="n">
-        <v>654370</v>
+        <v>1649295</v>
       </c>
       <c r="M21" t="n">
-        <v>1.81</v>
+        <v>0.89</v>
       </c>
       <c r="N21" t="n">
-        <v>15544.83422851562</v>
+        <v>87953.48413085938</v>
       </c>
       <c r="O21" t="n">
-        <v>675569</v>
+        <v>1672058</v>
       </c>
       <c r="P21" t="n">
-        <v>5.11</v>
+        <v>2.29</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.87841796875</v>
+        <v>32.044921875</v>
       </c>
       <c r="R21" t="n">
-        <v>675569</v>
+        <v>1672058</v>
       </c>
       <c r="S21" t="n">
-        <v>5.11</v>
+        <v>2.29</v>
       </c>
       <c r="T21" t="n">
-        <v>24961.74584960937</v>
+        <v>187869.6728515625</v>
       </c>
       <c r="U21" t="n">
-        <v>675569</v>
+        <v>1672058</v>
       </c>
       <c r="V21" t="n">
-        <v>5.11</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1x2x10</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2x10</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1x2x10 : 2x10</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>254.035888671875</v>
+        <v>319.741943359375</v>
       </c>
       <c r="F22" t="n">
-        <v>422832</v>
+        <v>639949</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.47900390625</v>
+        <v>0.90625</v>
       </c>
       <c r="I22" t="n">
-        <v>440123</v>
+        <v>668113</v>
       </c>
       <c r="J22" t="n">
-        <v>4.09</v>
+        <v>4.4</v>
       </c>
       <c r="K22" t="n">
-        <v>22.52490234375</v>
+        <v>122.519775390625</v>
       </c>
       <c r="L22" t="n">
-        <v>428258</v>
+        <v>649925</v>
       </c>
       <c r="M22" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="N22" t="n">
-        <v>8367.501953125</v>
+        <v>15431.255859375</v>
       </c>
       <c r="O22" t="n">
-        <v>442093</v>
+        <v>670090</v>
       </c>
       <c r="P22" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.257080078125</v>
+        <v>5.778076171875</v>
       </c>
       <c r="R22" t="n">
-        <v>442093</v>
+        <v>670090</v>
       </c>
       <c r="S22" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
       <c r="T22" t="n">
-        <v>10853.1162109375</v>
+        <v>24826.73510742188</v>
       </c>
       <c r="U22" t="n">
-        <v>442093</v>
+        <v>670090</v>
       </c>
       <c r="V22" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1x2x10</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2x10</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1x2x10 : 2x10</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>154.92578125</v>
+        <v>1079.265869140625</v>
       </c>
       <c r="F23" t="n">
-        <v>433885</v>
+        <v>631419</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.47802734375</v>
+        <v>0.908935546875</v>
       </c>
       <c r="I23" t="n">
-        <v>461941</v>
+        <v>658145</v>
       </c>
       <c r="J23" t="n">
-        <v>6.47</v>
+        <v>4.23</v>
       </c>
       <c r="K23" t="n">
-        <v>48.533447265625</v>
+        <v>74.822021484375</v>
       </c>
       <c r="L23" t="n">
-        <v>437212</v>
+        <v>639448</v>
       </c>
       <c r="M23" t="n">
-        <v>0.77</v>
+        <v>1.27</v>
       </c>
       <c r="N23" t="n">
-        <v>8259.89111328125</v>
+        <v>15450.43579101562</v>
       </c>
       <c r="O23" t="n">
-        <v>466489</v>
+        <v>658370</v>
       </c>
       <c r="P23" t="n">
-        <v>7.51</v>
+        <v>4.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35693359375</v>
+        <v>5.705810546875</v>
       </c>
       <c r="R23" t="n">
-        <v>466489</v>
+        <v>658370</v>
       </c>
       <c r="S23" t="n">
-        <v>7.51</v>
+        <v>4.27</v>
       </c>
       <c r="T23" t="n">
-        <v>10718.83276367188</v>
+        <v>24808.75390625</v>
       </c>
       <c r="U23" t="n">
-        <v>466489</v>
+        <v>658370</v>
       </c>
       <c r="V23" t="n">
-        <v>7.51</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1x2x10</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2x10</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1x2x10 : 2x10</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>404.15673828125</v>
+        <v>709.0712890625</v>
       </c>
       <c r="F24" t="n">
-        <v>431951</v>
+        <v>641082</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.469970703125</v>
+        <v>0.90234375</v>
       </c>
       <c r="I24" t="n">
-        <v>450812</v>
+        <v>672870</v>
       </c>
       <c r="J24" t="n">
-        <v>4.37</v>
+        <v>4.96</v>
       </c>
       <c r="K24" t="n">
-        <v>25.556884765625</v>
+        <v>99.365234375</v>
       </c>
       <c r="L24" t="n">
-        <v>438804</v>
+        <v>648058</v>
       </c>
       <c r="M24" t="n">
-        <v>1.59</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>8329.64599609375</v>
+        <v>15532.07666015625</v>
       </c>
       <c r="O24" t="n">
-        <v>444365</v>
+        <v>668949</v>
       </c>
       <c r="P24" t="n">
-        <v>2.87</v>
+        <v>4.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.30712890625</v>
+        <v>5.762939453125</v>
       </c>
       <c r="R24" t="n">
-        <v>444365</v>
+        <v>668949</v>
       </c>
       <c r="S24" t="n">
-        <v>2.87</v>
+        <v>4.35</v>
       </c>
       <c r="T24" t="n">
-        <v>10751.58374023438</v>
+        <v>24798.31591796875</v>
       </c>
       <c r="U24" t="n">
-        <v>444365</v>
+        <v>668949</v>
       </c>
       <c r="V24" t="n">
-        <v>2.87</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1x2x10</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2x10</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1x2x10 : 2x10</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>200.6669921875</v>
+        <v>399.50390625</v>
       </c>
       <c r="F25" t="n">
-        <v>435598</v>
+        <v>642479</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.595947265625</v>
+        <v>0.980224609375</v>
       </c>
       <c r="I25" t="n">
-        <v>454495</v>
+        <v>671571</v>
       </c>
       <c r="J25" t="n">
-        <v>4.34</v>
+        <v>4.53</v>
       </c>
       <c r="K25" t="n">
-        <v>65.01025390625</v>
+        <v>87.03173828125</v>
       </c>
       <c r="L25" t="n">
-        <v>441836</v>
+        <v>654440</v>
       </c>
       <c r="M25" t="n">
-        <v>1.43</v>
+        <v>1.86</v>
       </c>
       <c r="N25" t="n">
-        <v>8432.498046875</v>
+        <v>15441.89331054688</v>
       </c>
       <c r="O25" t="n">
-        <v>460142</v>
+        <v>668259</v>
       </c>
       <c r="P25" t="n">
-        <v>5.63</v>
+        <v>4.01</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.339111328125</v>
+        <v>5.765380859375</v>
       </c>
       <c r="R25" t="n">
-        <v>460142</v>
+        <v>668259</v>
       </c>
       <c r="S25" t="n">
-        <v>5.63</v>
+        <v>4.01</v>
       </c>
       <c r="T25" t="n">
-        <v>10867.04125976562</v>
+        <v>24855.16015625</v>
       </c>
       <c r="U25" t="n">
-        <v>460142</v>
+        <v>668259</v>
       </c>
       <c r="V25" t="n">
-        <v>5.63</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1x2x10</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2x10</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1x2x10 : 2x10</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>218.751953125</v>
+        <v>403.687744140625</v>
       </c>
       <c r="F26" t="n">
-        <v>434772</v>
+        <v>640704</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.475830078125</v>
+        <v>0.929931640625</v>
       </c>
       <c r="I26" t="n">
-        <v>454573</v>
+        <v>669479</v>
       </c>
       <c r="J26" t="n">
-        <v>4.55</v>
+        <v>4.49</v>
       </c>
       <c r="K26" t="n">
-        <v>39.2509765625</v>
+        <v>166.362548828125</v>
       </c>
       <c r="L26" t="n">
-        <v>439579</v>
+        <v>648286</v>
       </c>
       <c r="M26" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="N26" t="n">
-        <v>8333.575927734375</v>
+        <v>15483.830078125</v>
       </c>
       <c r="O26" t="n">
-        <v>460111</v>
+        <v>669105</v>
       </c>
       <c r="P26" t="n">
-        <v>5.83</v>
+        <v>4.43</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2587890625</v>
+        <v>5.701171875</v>
       </c>
       <c r="R26" t="n">
-        <v>460111</v>
+        <v>669105</v>
       </c>
       <c r="S26" t="n">
-        <v>5.83</v>
+        <v>4.43</v>
       </c>
       <c r="T26" t="n">
-        <v>10744.55615234375</v>
+        <v>24804.92114257812</v>
       </c>
       <c r="U26" t="n">
-        <v>460111</v>
+        <v>669105</v>
       </c>
       <c r="V26" t="n">
-        <v>5.83</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1x2x10</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2x10</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1x2x10 : 2x10</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>198.788330078125</v>
+        <v>650.97216796875</v>
       </c>
       <c r="F27" t="n">
-        <v>441754</v>
+        <v>639093</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.47802734375</v>
+        <v>0.932861328125</v>
       </c>
       <c r="I27" t="n">
-        <v>471346</v>
+        <v>652383</v>
       </c>
       <c r="J27" t="n">
-        <v>6.7</v>
+        <v>2.08</v>
       </c>
       <c r="K27" t="n">
-        <v>28.769775390625</v>
+        <v>68.56494140625</v>
       </c>
       <c r="L27" t="n">
-        <v>446735</v>
+        <v>646189</v>
       </c>
       <c r="M27" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N27" t="n">
-        <v>8284.93505859375</v>
+        <v>15568.84814453125</v>
       </c>
       <c r="O27" t="n">
-        <v>470544</v>
+        <v>652383</v>
       </c>
       <c r="P27" t="n">
-        <v>6.52</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.294189453125</v>
+        <v>5.81103515625</v>
       </c>
       <c r="R27" t="n">
-        <v>470544</v>
+        <v>652383</v>
       </c>
       <c r="S27" t="n">
-        <v>6.52</v>
+        <v>2.08</v>
       </c>
       <c r="T27" t="n">
-        <v>10765.58813476562</v>
+        <v>24946.951171875</v>
       </c>
       <c r="U27" t="n">
-        <v>470544</v>
+        <v>652383</v>
       </c>
       <c r="V27" t="n">
-        <v>6.52</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1x2x10</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2x10</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1x2x10 : 2x10</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>211.4580078125</v>
+        <v>327.651123046875</v>
       </c>
       <c r="F28" t="n">
-        <v>443879</v>
+        <v>642152</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.493896484375</v>
+        <v>0.9140625</v>
       </c>
       <c r="I28" t="n">
-        <v>469001</v>
+        <v>663737</v>
       </c>
       <c r="J28" t="n">
-        <v>5.66</v>
+        <v>3.36</v>
       </c>
       <c r="K28" t="n">
-        <v>37.51904296875</v>
+        <v>129.13623046875</v>
       </c>
       <c r="L28" t="n">
-        <v>447700</v>
+        <v>647996</v>
       </c>
       <c r="M28" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="N28" t="n">
-        <v>8355.719482421875</v>
+        <v>15506.2626953125</v>
       </c>
       <c r="O28" t="n">
-        <v>466335</v>
+        <v>678045</v>
       </c>
       <c r="P28" t="n">
-        <v>5.06</v>
+        <v>5.59</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.93505859375</v>
+        <v>5.822998046875</v>
       </c>
       <c r="R28" t="n">
-        <v>466335</v>
+        <v>678045</v>
       </c>
       <c r="S28" t="n">
-        <v>5.06</v>
+        <v>5.59</v>
       </c>
       <c r="T28" t="n">
-        <v>10769.27392578125</v>
+        <v>24951.0146484375</v>
       </c>
       <c r="U28" t="n">
-        <v>466335</v>
+        <v>678045</v>
       </c>
       <c r="V28" t="n">
-        <v>5.06</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1x2x10</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2x10</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1x2x10 : 2x10</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>157.81103515625</v>
+        <v>472.299072265625</v>
       </c>
       <c r="F29" t="n">
-        <v>443200</v>
+        <v>639061</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.48486328125</v>
+        <v>0.90380859375</v>
       </c>
       <c r="I29" t="n">
-        <v>477135</v>
+        <v>674969</v>
       </c>
       <c r="J29" t="n">
-        <v>7.66</v>
+        <v>5.62</v>
       </c>
       <c r="K29" t="n">
-        <v>46.580810546875</v>
+        <v>161.4091796875</v>
       </c>
       <c r="L29" t="n">
-        <v>446271</v>
+        <v>646653</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="N29" t="n">
-        <v>8306.42822265625</v>
+        <v>15604.94311523438</v>
       </c>
       <c r="O29" t="n">
-        <v>475192</v>
+        <v>674969</v>
       </c>
       <c r="P29" t="n">
-        <v>7.22</v>
+        <v>5.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.31298828125</v>
+        <v>5.899169921875</v>
       </c>
       <c r="R29" t="n">
-        <v>475192</v>
+        <v>674969</v>
       </c>
       <c r="S29" t="n">
-        <v>7.22</v>
+        <v>5.62</v>
       </c>
       <c r="T29" t="n">
-        <v>10672.65698242188</v>
+        <v>24852.47509765625</v>
       </c>
       <c r="U29" t="n">
-        <v>475192</v>
+        <v>674969</v>
       </c>
       <c r="V29" t="n">
-        <v>7.22</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1x2x10</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2x10</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1x2x10 : 2x10</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>803.43701171875</v>
+        <v>398.55615234375</v>
       </c>
       <c r="F30" t="n">
-        <v>437225</v>
+        <v>632255</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5107421875</v>
+        <v>0.930908203125</v>
       </c>
       <c r="I30" t="n">
-        <v>457610</v>
+        <v>670269</v>
       </c>
       <c r="J30" t="n">
-        <v>4.66</v>
+        <v>6.01</v>
       </c>
       <c r="K30" t="n">
-        <v>21.85009765625</v>
+        <v>199.89306640625</v>
       </c>
       <c r="L30" t="n">
-        <v>448246</v>
+        <v>635039</v>
       </c>
       <c r="M30" t="n">
-        <v>2.52</v>
+        <v>0.44</v>
       </c>
       <c r="N30" t="n">
-        <v>8267.98681640625</v>
+        <v>15590.544921875</v>
       </c>
       <c r="O30" t="n">
-        <v>457610</v>
+        <v>651592</v>
       </c>
       <c r="P30" t="n">
-        <v>4.66</v>
+        <v>3.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.413818359375</v>
+        <v>5.841064453125</v>
       </c>
       <c r="R30" t="n">
-        <v>457610</v>
+        <v>651592</v>
       </c>
       <c r="S30" t="n">
-        <v>4.66</v>
+        <v>3.06</v>
       </c>
       <c r="T30" t="n">
-        <v>10795.875</v>
+        <v>24958.20288085937</v>
       </c>
       <c r="U30" t="n">
-        <v>457610</v>
+        <v>651592</v>
       </c>
       <c r="V30" t="n">
-        <v>4.66</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1x2x10</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2x10</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1x2x10 : 2x10</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>207.4560546875</v>
+        <v>328.806884765625</v>
       </c>
       <c r="F31" t="n">
-        <v>444241</v>
+        <v>642737</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.481689453125</v>
+        <v>0.9130859375</v>
       </c>
       <c r="I31" t="n">
-        <v>461164</v>
+        <v>674436</v>
       </c>
       <c r="J31" t="n">
-        <v>3.81</v>
+        <v>4.93</v>
       </c>
       <c r="K31" t="n">
-        <v>51.103759765625</v>
+        <v>85.758056640625</v>
       </c>
       <c r="L31" t="n">
-        <v>447842</v>
+        <v>654370</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.81</v>
       </c>
       <c r="N31" t="n">
-        <v>8277.3671875</v>
+        <v>15544.83422851562</v>
       </c>
       <c r="O31" t="n">
-        <v>465627</v>
+        <v>675569</v>
       </c>
       <c r="P31" t="n">
-        <v>4.81</v>
+        <v>5.11</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.348876953125</v>
+        <v>5.87841796875</v>
       </c>
       <c r="R31" t="n">
-        <v>465627</v>
+        <v>675569</v>
       </c>
       <c r="S31" t="n">
-        <v>4.81</v>
+        <v>5.11</v>
       </c>
       <c r="T31" t="n">
-        <v>10651.22192382812</v>
+        <v>24961.74584960937</v>
       </c>
       <c r="U31" t="n">
-        <v>465627</v>
+        <v>675569</v>
       </c>
       <c r="V31" t="n">
-        <v>4.81</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x10 : 2x10</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>68.346923828125</v>
+        <v>254.035888671875</v>
       </c>
       <c r="F32" t="n">
-        <v>230169</v>
+        <v>422832</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1982421875</v>
+        <v>0.47900390625</v>
       </c>
       <c r="I32" t="n">
-        <v>239494</v>
+        <v>440123</v>
       </c>
       <c r="J32" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="K32" t="n">
-        <v>1.58203125</v>
+        <v>22.52490234375</v>
       </c>
       <c r="L32" t="n">
-        <v>237778</v>
+        <v>428258</v>
       </c>
       <c r="M32" t="n">
-        <v>3.31</v>
+        <v>1.28</v>
       </c>
       <c r="N32" t="n">
-        <v>3073.056884765625</v>
+        <v>8367.501953125</v>
       </c>
       <c r="O32" t="n">
-        <v>239494</v>
+        <v>442093</v>
       </c>
       <c r="P32" t="n">
-        <v>4.05</v>
+        <v>4.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.56591796875</v>
+        <v>3.257080078125</v>
       </c>
       <c r="R32" t="n">
-        <v>239494</v>
+        <v>442093</v>
       </c>
       <c r="S32" t="n">
-        <v>4.05</v>
+        <v>4.56</v>
       </c>
       <c r="T32" t="n">
-        <v>2350.739990234375</v>
+        <v>10853.1162109375</v>
       </c>
       <c r="U32" t="n">
-        <v>239494</v>
+        <v>442093</v>
       </c>
       <c r="V32" t="n">
-        <v>4.05</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x10 : 2x10</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>69.915283203125</v>
+        <v>154.92578125</v>
       </c>
       <c r="F33" t="n">
-        <v>233930</v>
+        <v>433885</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.18505859375</v>
+        <v>0.47802734375</v>
       </c>
       <c r="I33" t="n">
-        <v>245162</v>
+        <v>461941</v>
       </c>
       <c r="J33" t="n">
-        <v>4.8</v>
+        <v>6.47</v>
       </c>
       <c r="K33" t="n">
-        <v>3.927978515625</v>
+        <v>48.533447265625</v>
       </c>
       <c r="L33" t="n">
-        <v>240371</v>
+        <v>437212</v>
       </c>
       <c r="M33" t="n">
-        <v>2.75</v>
+        <v>0.77</v>
       </c>
       <c r="N33" t="n">
-        <v>3070.212646484375</v>
+        <v>8259.89111328125</v>
       </c>
       <c r="O33" t="n">
-        <v>248738</v>
+        <v>466489</v>
       </c>
       <c r="P33" t="n">
-        <v>6.33</v>
+        <v>7.51</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.679931640625</v>
+        <v>3.35693359375</v>
       </c>
       <c r="R33" t="n">
-        <v>248738</v>
+        <v>466489</v>
       </c>
       <c r="S33" t="n">
-        <v>6.33</v>
+        <v>7.51</v>
       </c>
       <c r="T33" t="n">
-        <v>2350.55224609375</v>
+        <v>10718.83276367188</v>
       </c>
       <c r="U33" t="n">
-        <v>248738</v>
+        <v>466489</v>
       </c>
       <c r="V33" t="n">
-        <v>6.33</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x10 : 2x10</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>71.02978515625</v>
+        <v>404.15673828125</v>
       </c>
       <c r="F34" t="n">
-        <v>236799</v>
+        <v>431951</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.17822265625</v>
+        <v>0.469970703125</v>
       </c>
       <c r="I34" t="n">
-        <v>261096</v>
+        <v>450812</v>
       </c>
       <c r="J34" t="n">
-        <v>10.26</v>
+        <v>4.37</v>
       </c>
       <c r="K34" t="n">
-        <v>7.503173828125</v>
+        <v>25.556884765625</v>
       </c>
       <c r="L34" t="n">
-        <v>240011</v>
+        <v>438804</v>
       </c>
       <c r="M34" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="N34" t="n">
-        <v>3139.3427734375</v>
+        <v>8329.64599609375</v>
       </c>
       <c r="O34" t="n">
-        <v>261096</v>
+        <v>444365</v>
       </c>
       <c r="P34" t="n">
-        <v>10.26</v>
+        <v>2.87</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.509765625</v>
+        <v>3.30712890625</v>
       </c>
       <c r="R34" t="n">
-        <v>261096</v>
+        <v>444365</v>
       </c>
       <c r="S34" t="n">
-        <v>10.26</v>
+        <v>2.87</v>
       </c>
       <c r="T34" t="n">
-        <v>2362.138916015625</v>
+        <v>10751.58374023438</v>
       </c>
       <c r="U34" t="n">
-        <v>261096</v>
+        <v>444365</v>
       </c>
       <c r="V34" t="n">
-        <v>10.26</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x10 : 2x10</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>64.52685546875</v>
+        <v>200.6669921875</v>
       </c>
       <c r="F35" t="n">
-        <v>237613</v>
+        <v>435598</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.18017578125</v>
+        <v>0.595947265625</v>
       </c>
       <c r="I35" t="n">
-        <v>249169</v>
+        <v>454495</v>
       </c>
       <c r="J35" t="n">
-        <v>4.86</v>
+        <v>4.34</v>
       </c>
       <c r="K35" t="n">
-        <v>3.831298828125</v>
+        <v>65.01025390625</v>
       </c>
       <c r="L35" t="n">
-        <v>240044</v>
+        <v>441836</v>
       </c>
       <c r="M35" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="N35" t="n">
-        <v>3034.0517578125</v>
+        <v>8432.498046875</v>
       </c>
       <c r="O35" t="n">
-        <v>249169</v>
+        <v>460142</v>
       </c>
       <c r="P35" t="n">
-        <v>4.86</v>
+        <v>5.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.527099609375</v>
+        <v>3.339111328125</v>
       </c>
       <c r="R35" t="n">
-        <v>249169</v>
+        <v>460142</v>
       </c>
       <c r="S35" t="n">
-        <v>4.86</v>
+        <v>5.63</v>
       </c>
       <c r="T35" t="n">
-        <v>2342.658203125</v>
+        <v>10867.04125976562</v>
       </c>
       <c r="U35" t="n">
-        <v>249169</v>
+        <v>460142</v>
       </c>
       <c r="V35" t="n">
-        <v>4.86</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x10 : 2x10</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>111.61279296875</v>
+        <v>218.751953125</v>
       </c>
       <c r="F36" t="n">
-        <v>226279</v>
+        <v>434772</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.187255859375</v>
+        <v>0.475830078125</v>
       </c>
       <c r="I36" t="n">
-        <v>228835</v>
+        <v>454573</v>
       </c>
       <c r="J36" t="n">
-        <v>1.13</v>
+        <v>4.55</v>
       </c>
       <c r="K36" t="n">
-        <v>0.757080078125</v>
+        <v>39.2509765625</v>
       </c>
       <c r="L36" t="n">
-        <v>228835</v>
+        <v>439579</v>
       </c>
       <c r="M36" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N36" t="n">
-        <v>3054.256103515625</v>
+        <v>8333.575927734375</v>
       </c>
       <c r="O36" t="n">
-        <v>237594</v>
+        <v>460111</v>
       </c>
       <c r="P36" t="n">
-        <v>5</v>
+        <v>5.83</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.539794921875</v>
+        <v>3.2587890625</v>
       </c>
       <c r="R36" t="n">
-        <v>237594</v>
+        <v>460111</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>5.83</v>
       </c>
       <c r="T36" t="n">
-        <v>2357.47802734375</v>
+        <v>10744.55615234375</v>
       </c>
       <c r="U36" t="n">
-        <v>237594</v>
+        <v>460111</v>
       </c>
       <c r="V36" t="n">
-        <v>5</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x10 : 2x10</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>66.020751953125</v>
+        <v>198.788330078125</v>
       </c>
       <c r="F37" t="n">
-        <v>236477</v>
+        <v>441754</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.18017578125</v>
+        <v>0.47802734375</v>
       </c>
       <c r="I37" t="n">
-        <v>246470</v>
+        <v>471346</v>
       </c>
       <c r="J37" t="n">
-        <v>4.23</v>
+        <v>6.7</v>
       </c>
       <c r="K37" t="n">
-        <v>3.884033203125</v>
+        <v>28.769775390625</v>
       </c>
       <c r="L37" t="n">
-        <v>238419</v>
+        <v>446735</v>
       </c>
       <c r="M37" t="n">
-        <v>0.82</v>
+        <v>1.13</v>
       </c>
       <c r="N37" t="n">
-        <v>3047.932861328125</v>
+        <v>8284.93505859375</v>
       </c>
       <c r="O37" t="n">
-        <v>256994</v>
+        <v>470544</v>
       </c>
       <c r="P37" t="n">
-        <v>8.68</v>
+        <v>6.52</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.527587890625</v>
+        <v>3.294189453125</v>
       </c>
       <c r="R37" t="n">
-        <v>256994</v>
+        <v>470544</v>
       </c>
       <c r="S37" t="n">
-        <v>8.68</v>
+        <v>6.52</v>
       </c>
       <c r="T37" t="n">
-        <v>2350.77099609375</v>
+        <v>10765.58813476562</v>
       </c>
       <c r="U37" t="n">
-        <v>256994</v>
+        <v>470544</v>
       </c>
       <c r="V37" t="n">
-        <v>8.68</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x10 : 2x10</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>115.257080078125</v>
+        <v>211.4580078125</v>
       </c>
       <c r="F38" t="n">
-        <v>238345</v>
+        <v>443879</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.187255859375</v>
+        <v>0.493896484375</v>
       </c>
       <c r="I38" t="n">
-        <v>246095</v>
+        <v>469001</v>
       </c>
       <c r="J38" t="n">
-        <v>3.25</v>
+        <v>5.66</v>
       </c>
       <c r="K38" t="n">
-        <v>5.14794921875</v>
+        <v>37.51904296875</v>
       </c>
       <c r="L38" t="n">
-        <v>239213</v>
+        <v>447700</v>
       </c>
       <c r="M38" t="n">
-        <v>0.36</v>
+        <v>0.86</v>
       </c>
       <c r="N38" t="n">
-        <v>3031.940185546875</v>
+        <v>8355.719482421875</v>
       </c>
       <c r="O38" t="n">
-        <v>251891</v>
+        <v>466335</v>
       </c>
       <c r="P38" t="n">
-        <v>5.68</v>
+        <v>5.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.625</v>
+        <v>3.93505859375</v>
       </c>
       <c r="R38" t="n">
-        <v>251891</v>
+        <v>466335</v>
       </c>
       <c r="S38" t="n">
-        <v>5.68</v>
+        <v>5.06</v>
       </c>
       <c r="T38" t="n">
-        <v>2338.601806640625</v>
+        <v>10769.27392578125</v>
       </c>
       <c r="U38" t="n">
-        <v>251891</v>
+        <v>466335</v>
       </c>
       <c r="V38" t="n">
-        <v>5.68</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x10 : 2x10</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>89.825927734375</v>
+        <v>157.81103515625</v>
       </c>
       <c r="F39" t="n">
-        <v>230678</v>
+        <v>443200</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.179931640625</v>
+        <v>0.48486328125</v>
       </c>
       <c r="I39" t="n">
-        <v>244385</v>
+        <v>477135</v>
       </c>
       <c r="J39" t="n">
-        <v>5.94</v>
+        <v>7.66</v>
       </c>
       <c r="K39" t="n">
-        <v>2.2216796875</v>
+        <v>46.580810546875</v>
       </c>
       <c r="L39" t="n">
-        <v>236044</v>
+        <v>446271</v>
       </c>
       <c r="M39" t="n">
-        <v>2.33</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>3075.974365234375</v>
+        <v>8306.42822265625</v>
       </c>
       <c r="O39" t="n">
-        <v>249374</v>
+        <v>475192</v>
       </c>
       <c r="P39" t="n">
-        <v>8.1</v>
+        <v>7.22</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.544921875</v>
+        <v>3.31298828125</v>
       </c>
       <c r="R39" t="n">
-        <v>249374</v>
+        <v>475192</v>
       </c>
       <c r="S39" t="n">
-        <v>8.1</v>
+        <v>7.22</v>
       </c>
       <c r="T39" t="n">
-        <v>2357.47412109375</v>
+        <v>10672.65698242188</v>
       </c>
       <c r="U39" t="n">
-        <v>249374</v>
+        <v>475192</v>
       </c>
       <c r="V39" t="n">
-        <v>8.1</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x10 : 2x10</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>9</v>
       </c>
       <c r="E40" t="n">
-        <v>89.454833984375</v>
+        <v>803.43701171875</v>
       </c>
       <c r="F40" t="n">
-        <v>234381</v>
+        <v>437225</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.192138671875</v>
+        <v>0.5107421875</v>
       </c>
       <c r="I40" t="n">
-        <v>254269</v>
+        <v>457610</v>
       </c>
       <c r="J40" t="n">
-        <v>8.49</v>
+        <v>4.66</v>
       </c>
       <c r="K40" t="n">
-        <v>8.2529296875</v>
+        <v>21.85009765625</v>
       </c>
       <c r="L40" t="n">
-        <v>236505</v>
+        <v>448246</v>
       </c>
       <c r="M40" t="n">
-        <v>0.91</v>
+        <v>2.52</v>
       </c>
       <c r="N40" t="n">
-        <v>3076.169921875</v>
+        <v>8267.98681640625</v>
       </c>
       <c r="O40" t="n">
-        <v>255289</v>
+        <v>457610</v>
       </c>
       <c r="P40" t="n">
-        <v>8.92</v>
+        <v>4.66</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.82373046875</v>
+        <v>3.413818359375</v>
       </c>
       <c r="R40" t="n">
-        <v>255289</v>
+        <v>457610</v>
       </c>
       <c r="S40" t="n">
-        <v>8.92</v>
+        <v>4.66</v>
       </c>
       <c r="T40" t="n">
-        <v>2351.128173828125</v>
+        <v>10795.875</v>
       </c>
       <c r="U40" t="n">
-        <v>255289</v>
+        <v>457610</v>
       </c>
       <c r="V40" t="n">
-        <v>8.92</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x10 : 2x10</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>91.505859375</v>
+        <v>207.4560546875</v>
       </c>
       <c r="F41" t="n">
-        <v>235877</v>
+        <v>444241</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.176025390625</v>
+        <v>0.481689453125</v>
       </c>
       <c r="I41" t="n">
-        <v>244795</v>
+        <v>461164</v>
       </c>
       <c r="J41" t="n">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="K41" t="n">
-        <v>4.78125</v>
+        <v>51.103759765625</v>
       </c>
       <c r="L41" t="n">
-        <v>236939</v>
+        <v>447842</v>
       </c>
       <c r="M41" t="n">
-        <v>0.45</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>3108.8466796875</v>
+        <v>8277.3671875</v>
       </c>
       <c r="O41" t="n">
-        <v>244795</v>
+        <v>465627</v>
       </c>
       <c r="P41" t="n">
-        <v>3.78</v>
+        <v>4.81</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.5888671875</v>
+        <v>3.348876953125</v>
       </c>
       <c r="R41" t="n">
-        <v>244795</v>
+        <v>465627</v>
       </c>
       <c r="S41" t="n">
-        <v>3.78</v>
+        <v>4.81</v>
       </c>
       <c r="T41" t="n">
-        <v>2336.68896484375</v>
+        <v>10651.22192382812</v>
       </c>
       <c r="U41" t="n">
-        <v>244795</v>
+        <v>465627</v>
       </c>
       <c r="V41" t="n">
-        <v>3.78</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1x2x45</t>
+          <t>1x2x5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2x45</t>
+          <t>2x5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1x2x45 : 2x45</t>
+          <t>1x2x5 : 2x5</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>9509.633056640623</v>
+        <v>68.346923828125</v>
       </c>
       <c r="F42" t="n">
-        <v>1841879</v>
+        <v>230169</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>6.47607421875</v>
+        <v>0.1982421875</v>
       </c>
       <c r="I42" t="n">
-        <v>1884041</v>
+        <v>239494</v>
       </c>
       <c r="J42" t="n">
-        <v>2.29</v>
+        <v>4.05</v>
       </c>
       <c r="K42" t="n">
-        <v>5286.2958984375</v>
+        <v>1.58203125</v>
       </c>
       <c r="L42" t="n">
-        <v>1857078</v>
+        <v>237778</v>
       </c>
       <c r="M42" t="n">
-        <v>0.83</v>
+        <v>3.31</v>
       </c>
       <c r="N42" t="n">
-        <v>104364.4482421875</v>
+        <v>3073.056884765625</v>
       </c>
       <c r="O42" t="n">
-        <v>1881424</v>
+        <v>239494</v>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>4.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>39.18310546875</v>
+        <v>1.56591796875</v>
       </c>
       <c r="R42" t="n">
-        <v>1881424</v>
+        <v>239494</v>
       </c>
       <c r="S42" t="n">
-        <v>2.15</v>
+        <v>4.05</v>
       </c>
       <c r="T42" t="n">
-        <v>241359.6369628907</v>
+        <v>2350.739990234375</v>
       </c>
       <c r="U42" t="n">
-        <v>1881424</v>
+        <v>239494</v>
       </c>
       <c r="V42" t="n">
-        <v>2.15</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1x2x45</t>
+          <t>1x2x5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2x45</t>
+          <t>2x5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1x2x45 : 2x45</t>
+          <t>1x2x5 : 2x5</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>9036.947998046877</v>
+        <v>69.915283203125</v>
       </c>
       <c r="F43" t="n">
-        <v>1840093</v>
+        <v>233930</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>6.433837890625</v>
+        <v>0.18505859375</v>
       </c>
       <c r="I43" t="n">
-        <v>1889362</v>
+        <v>245162</v>
       </c>
       <c r="J43" t="n">
-        <v>2.68</v>
+        <v>4.8</v>
       </c>
       <c r="K43" t="n">
-        <v>10058.42626953125</v>
+        <v>3.927978515625</v>
       </c>
       <c r="L43" t="n">
-        <v>1856770</v>
+        <v>240371</v>
       </c>
       <c r="M43" t="n">
-        <v>0.91</v>
+        <v>2.75</v>
       </c>
       <c r="N43" t="n">
-        <v>104905.7021484375</v>
+        <v>3070.212646484375</v>
       </c>
       <c r="O43" t="n">
-        <v>1890431</v>
+        <v>248738</v>
       </c>
       <c r="P43" t="n">
-        <v>2.74</v>
+        <v>6.33</v>
       </c>
       <c r="Q43" t="n">
-        <v>38.452880859375</v>
+        <v>1.679931640625</v>
       </c>
       <c r="R43" t="n">
-        <v>1890431</v>
+        <v>248738</v>
       </c>
       <c r="S43" t="n">
-        <v>2.74</v>
+        <v>6.33</v>
       </c>
       <c r="T43" t="n">
-        <v>240401.2668457031</v>
+        <v>2350.55224609375</v>
       </c>
       <c r="U43" t="n">
-        <v>1890431</v>
+        <v>248738</v>
       </c>
       <c r="V43" t="n">
-        <v>2.74</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1x2x45</t>
+          <t>1x2x5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2x45</t>
+          <t>2x5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1x2x45 : 2x45</t>
+          <t>1x2x5 : 2x5</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>10161.15869140625</v>
+        <v>71.02978515625</v>
       </c>
       <c r="F44" t="n">
-        <v>1843452</v>
+        <v>236799</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>7.19677734375</v>
+        <v>0.17822265625</v>
       </c>
       <c r="I44" t="n">
-        <v>1893865</v>
+        <v>261096</v>
       </c>
       <c r="J44" t="n">
-        <v>2.73</v>
+        <v>10.26</v>
       </c>
       <c r="K44" t="n">
-        <v>8871.572021484375</v>
+        <v>7.503173828125</v>
       </c>
       <c r="L44" t="n">
-        <v>1854780</v>
+        <v>240011</v>
       </c>
       <c r="M44" t="n">
-        <v>0.61</v>
+        <v>1.36</v>
       </c>
       <c r="N44" t="n">
-        <v>104245.921875</v>
+        <v>3139.3427734375</v>
       </c>
       <c r="O44" t="n">
-        <v>1895230</v>
+        <v>261096</v>
       </c>
       <c r="P44" t="n">
-        <v>2.81</v>
+        <v>10.26</v>
       </c>
       <c r="Q44" t="n">
-        <v>39.606689453125</v>
+        <v>1.509765625</v>
       </c>
       <c r="R44" t="n">
-        <v>1895230</v>
+        <v>261096</v>
       </c>
       <c r="S44" t="n">
-        <v>2.81</v>
+        <v>10.26</v>
       </c>
       <c r="T44" t="n">
-        <v>240154.9807128907</v>
+        <v>2362.138916015625</v>
       </c>
       <c r="U44" t="n">
-        <v>1895230</v>
+        <v>261096</v>
       </c>
       <c r="V44" t="n">
-        <v>2.81</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1x2x45</t>
+          <t>1x2x5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2x45</t>
+          <t>2x5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1x2x45 : 2x45</t>
+          <t>1x2x5 : 2x5</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>23118.60595703125</v>
+        <v>64.52685546875</v>
       </c>
       <c r="F45" t="n">
-        <v>1834797</v>
+        <v>237613</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>6.7216796875</v>
+        <v>0.18017578125</v>
       </c>
       <c r="I45" t="n">
-        <v>1876683</v>
+        <v>249169</v>
       </c>
       <c r="J45" t="n">
-        <v>2.28</v>
+        <v>4.86</v>
       </c>
       <c r="K45" t="n">
-        <v>7479.30517578125</v>
+        <v>3.831298828125</v>
       </c>
       <c r="L45" t="n">
-        <v>1848658</v>
+        <v>240044</v>
       </c>
       <c r="M45" t="n">
-        <v>0.76</v>
+        <v>1.02</v>
       </c>
       <c r="N45" t="n">
-        <v>104550.0661621094</v>
+        <v>3034.0517578125</v>
       </c>
       <c r="O45" t="n">
-        <v>1872135</v>
+        <v>249169</v>
       </c>
       <c r="P45" t="n">
-        <v>2.03</v>
+        <v>4.86</v>
       </c>
       <c r="Q45" t="n">
-        <v>38.36181640625</v>
+        <v>1.527099609375</v>
       </c>
       <c r="R45" t="n">
-        <v>1872135</v>
+        <v>249169</v>
       </c>
       <c r="S45" t="n">
-        <v>2.03</v>
+        <v>4.86</v>
       </c>
       <c r="T45" t="n">
-        <v>240625.6577148437</v>
+        <v>2342.658203125</v>
       </c>
       <c r="U45" t="n">
-        <v>1872135</v>
+        <v>249169</v>
       </c>
       <c r="V45" t="n">
-        <v>2.03</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1x2x45</t>
+          <t>1x2x5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2x45</t>
+          <t>2x5</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1x2x45 : 2x45</t>
+          <t>1x2x5 : 2x5</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>10</v>
       </c>
       <c r="E46" t="n">
-        <v>8149.406005859375</v>
+        <v>111.61279296875</v>
       </c>
       <c r="F46" t="n">
-        <v>1842609</v>
+        <v>226279</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>7.934326171875</v>
+        <v>0.187255859375</v>
       </c>
       <c r="I46" t="n">
-        <v>1875292</v>
+        <v>228835</v>
       </c>
       <c r="J46" t="n">
-        <v>1.77</v>
+        <v>1.13</v>
       </c>
       <c r="K46" t="n">
-        <v>6122.878173828125</v>
+        <v>0.757080078125</v>
       </c>
       <c r="L46" t="n">
-        <v>1856664</v>
+        <v>228835</v>
       </c>
       <c r="M46" t="n">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="N46" t="n">
-        <v>104193.8342285156</v>
+        <v>3054.256103515625</v>
       </c>
       <c r="O46" t="n">
-        <v>1884846</v>
+        <v>237594</v>
       </c>
       <c r="P46" t="n">
-        <v>2.29</v>
+        <v>5</v>
       </c>
       <c r="Q46" t="n">
-        <v>39.9697265625</v>
+        <v>1.539794921875</v>
       </c>
       <c r="R46" t="n">
-        <v>1884846</v>
+        <v>237594</v>
       </c>
       <c r="S46" t="n">
-        <v>2.29</v>
+        <v>5</v>
       </c>
       <c r="T46" t="n">
-        <v>240206.2219238281</v>
+        <v>2357.47802734375</v>
       </c>
       <c r="U46" t="n">
-        <v>1884846</v>
+        <v>237594</v>
       </c>
       <c r="V46" t="n">
-        <v>2.29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1x2x45</t>
+          <t>1x2x5</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2x45</t>
+          <t>2x5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1x2x45 : 2x45</t>
+          <t>1x2x5 : 2x5</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>22064.2998046875</v>
+        <v>66.020751953125</v>
       </c>
       <c r="F47" t="n">
-        <v>1834850</v>
+        <v>236477</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>7.202880859375</v>
+        <v>0.18017578125</v>
       </c>
       <c r="I47" t="n">
-        <v>1864442</v>
+        <v>246470</v>
       </c>
       <c r="J47" t="n">
-        <v>1.61</v>
+        <v>4.23</v>
       </c>
       <c r="K47" t="n">
-        <v>4480.68701171875</v>
+        <v>3.884033203125</v>
       </c>
       <c r="L47" t="n">
-        <v>1845291</v>
+        <v>238419</v>
       </c>
       <c r="M47" t="n">
-        <v>0.57</v>
+        <v>0.82</v>
       </c>
       <c r="N47" t="n">
-        <v>104671.0942382812</v>
+        <v>3047.932861328125</v>
       </c>
       <c r="O47" t="n">
-        <v>1889142</v>
+        <v>256994</v>
       </c>
       <c r="P47" t="n">
-        <v>2.96</v>
+        <v>8.68</v>
       </c>
       <c r="Q47" t="n">
-        <v>39.5029296875</v>
+        <v>1.527587890625</v>
       </c>
       <c r="R47" t="n">
-        <v>1889142</v>
+        <v>256994</v>
       </c>
       <c r="S47" t="n">
-        <v>2.96</v>
+        <v>8.68</v>
       </c>
       <c r="T47" t="n">
-        <v>239663.3186035156</v>
+        <v>2350.77099609375</v>
       </c>
       <c r="U47" t="n">
-        <v>1889142</v>
+        <v>256994</v>
       </c>
       <c r="V47" t="n">
-        <v>2.96</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1x2x45</t>
+          <t>1x2x5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2x45</t>
+          <t>2x5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1x2x45 : 2x45</t>
+          <t>1x2x5 : 2x5</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>12025.453125</v>
+        <v>115.257080078125</v>
       </c>
       <c r="F48" t="n">
-        <v>1835241</v>
+        <v>238345</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>6.502685546875</v>
+        <v>0.187255859375</v>
       </c>
       <c r="I48" t="n">
-        <v>1870630</v>
+        <v>246095</v>
       </c>
       <c r="J48" t="n">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="K48" t="n">
-        <v>5085.25390625</v>
+        <v>5.14794921875</v>
       </c>
       <c r="L48" t="n">
-        <v>1848776</v>
+        <v>239213</v>
       </c>
       <c r="M48" t="n">
-        <v>0.74</v>
+        <v>0.36</v>
       </c>
       <c r="N48" t="n">
-        <v>103949.5390625</v>
+        <v>3031.940185546875</v>
       </c>
       <c r="O48" t="n">
-        <v>1881803</v>
+        <v>251891</v>
       </c>
       <c r="P48" t="n">
-        <v>2.54</v>
+        <v>5.68</v>
       </c>
       <c r="Q48" t="n">
-        <v>39.079833984375</v>
+        <v>1.625</v>
       </c>
       <c r="R48" t="n">
-        <v>1881803</v>
+        <v>251891</v>
       </c>
       <c r="S48" t="n">
-        <v>2.54</v>
+        <v>5.68</v>
       </c>
       <c r="T48" t="n">
-        <v>241563.0029296875</v>
+        <v>2338.601806640625</v>
       </c>
       <c r="U48" t="n">
-        <v>1881803</v>
+        <v>251891</v>
       </c>
       <c r="V48" t="n">
-        <v>2.54</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1x2x45</t>
+          <t>1x2x5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2x45</t>
+          <t>2x5</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1x2x45 : 2x45</t>
+          <t>1x2x5 : 2x5</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>16908.37866210938</v>
+        <v>89.825927734375</v>
       </c>
       <c r="F49" t="n">
-        <v>1844624</v>
+        <v>230678</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>6.461181640625</v>
+        <v>0.179931640625</v>
       </c>
       <c r="I49" t="n">
-        <v>1892366</v>
+        <v>244385</v>
       </c>
       <c r="J49" t="n">
-        <v>2.59</v>
+        <v>5.94</v>
       </c>
       <c r="K49" t="n">
-        <v>5848.653076171875</v>
+        <v>2.2216796875</v>
       </c>
       <c r="L49" t="n">
-        <v>1860769</v>
+        <v>236044</v>
       </c>
       <c r="M49" t="n">
-        <v>0.88</v>
+        <v>2.33</v>
       </c>
       <c r="N49" t="n">
-        <v>104717.1369628906</v>
+        <v>3075.974365234375</v>
       </c>
       <c r="O49" t="n">
-        <v>1901089</v>
+        <v>249374</v>
       </c>
       <c r="P49" t="n">
-        <v>3.06</v>
+        <v>8.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>39.57177734375</v>
+        <v>1.544921875</v>
       </c>
       <c r="R49" t="n">
-        <v>1901089</v>
+        <v>249374</v>
       </c>
       <c r="S49" t="n">
-        <v>3.06</v>
+        <v>8.1</v>
       </c>
       <c r="T49" t="n">
-        <v>243138.447265625</v>
+        <v>2357.47412109375</v>
       </c>
       <c r="U49" t="n">
-        <v>1901089</v>
+        <v>249374</v>
       </c>
       <c r="V49" t="n">
-        <v>3.06</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1x2x45</t>
+          <t>1x2x5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2x45</t>
+          <t>2x5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1x2x45 : 2x45</t>
+          <t>1x2x5 : 2x5</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>12767.5283203125</v>
+        <v>89.454833984375</v>
       </c>
       <c r="F50" t="n">
-        <v>1839962</v>
+        <v>234381</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>7.414794921875</v>
+        <v>0.192138671875</v>
       </c>
       <c r="I50" t="n">
-        <v>1901727</v>
+        <v>254269</v>
       </c>
       <c r="J50" t="n">
-        <v>3.36</v>
+        <v>8.49</v>
       </c>
       <c r="K50" t="n">
-        <v>6991.81396484375</v>
+        <v>8.2529296875</v>
       </c>
       <c r="L50" t="n">
-        <v>1854619</v>
+        <v>236505</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="N50" t="n">
-        <v>105392.1430664062</v>
+        <v>3076.169921875</v>
       </c>
       <c r="O50" t="n">
-        <v>1883748</v>
+        <v>255289</v>
       </c>
       <c r="P50" t="n">
-        <v>2.38</v>
+        <v>8.92</v>
       </c>
       <c r="Q50" t="n">
-        <v>38.95703125</v>
+        <v>1.82373046875</v>
       </c>
       <c r="R50" t="n">
-        <v>1883748</v>
+        <v>255289</v>
       </c>
       <c r="S50" t="n">
-        <v>2.38</v>
+        <v>8.92</v>
       </c>
       <c r="T50" t="n">
-        <v>241795.580078125</v>
+        <v>2351.128173828125</v>
       </c>
       <c r="U50" t="n">
-        <v>1883748</v>
+        <v>255289</v>
       </c>
       <c r="V50" t="n">
-        <v>2.38</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1x2x45</t>
+          <t>1x2x5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2x45</t>
+          <t>2x5</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1x2x45 : 2x45</t>
+          <t>1x2x5 : 2x5</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v>7</v>
       </c>
       <c r="E51" t="n">
-        <v>18171.29614257812</v>
+        <v>91.505859375</v>
       </c>
       <c r="F51" t="n">
-        <v>1850376</v>
+        <v>235877</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>8.936767578125</v>
+        <v>0.176025390625</v>
       </c>
       <c r="I51" t="n">
-        <v>1897577</v>
+        <v>244795</v>
       </c>
       <c r="J51" t="n">
-        <v>2.55</v>
+        <v>3.78</v>
       </c>
       <c r="K51" t="n">
-        <v>9193.56689453125</v>
+        <v>4.78125</v>
       </c>
       <c r="L51" t="n">
-        <v>1862467</v>
+        <v>236939</v>
       </c>
       <c r="M51" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="N51" t="n">
-        <v>104196.3291015625</v>
+        <v>3108.8466796875</v>
       </c>
       <c r="O51" t="n">
-        <v>1913242</v>
+        <v>244795</v>
       </c>
       <c r="P51" t="n">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="Q51" t="n">
-        <v>40.10791015625</v>
+        <v>1.5888671875</v>
       </c>
       <c r="R51" t="n">
-        <v>1913242</v>
+        <v>244795</v>
       </c>
       <c r="S51" t="n">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="T51" t="n">
-        <v>239113.4672851562</v>
+        <v>2336.68896484375</v>
       </c>
       <c r="U51" t="n">
-        <v>1913242</v>
+        <v>244795</v>
       </c>
       <c r="V51" t="n">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1x2x35</t>
+          <t>1x2x45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2x35</t>
+          <t>2x45</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1x2x35 : 2x35</t>
+          <t>1x2x45 : 2x45</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>8759.420166015625</v>
+        <v>9509.633056640623</v>
       </c>
       <c r="F52" t="n">
-        <v>1441753</v>
+        <v>1841879</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>5.830810546875</v>
+        <v>6.47607421875</v>
       </c>
       <c r="I52" t="n">
-        <v>1483243</v>
+        <v>1884041</v>
       </c>
       <c r="J52" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="K52" t="n">
-        <v>2092.8388671875</v>
+        <v>5286.2958984375</v>
       </c>
       <c r="L52" t="n">
-        <v>1452833</v>
+        <v>1857078</v>
       </c>
       <c r="M52" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="N52" t="n">
-        <v>66502.51708984375</v>
+        <v>104364.4482421875</v>
       </c>
       <c r="O52" t="n">
-        <v>1491193</v>
+        <v>1881424</v>
       </c>
       <c r="P52" t="n">
-        <v>3.43</v>
+        <v>2.15</v>
       </c>
       <c r="Q52" t="n">
-        <v>24.9599609375</v>
+        <v>39.18310546875</v>
       </c>
       <c r="R52" t="n">
-        <v>1491193</v>
+        <v>1881424</v>
       </c>
       <c r="S52" t="n">
-        <v>3.43</v>
+        <v>2.15</v>
       </c>
       <c r="T52" t="n">
-        <v>144426.9968261719</v>
+        <v>241359.6369628907</v>
       </c>
       <c r="U52" t="n">
-        <v>1491193</v>
+        <v>1881424</v>
       </c>
       <c r="V52" t="n">
-        <v>3.43</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1x2x35</t>
+          <t>1x2x45</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2x35</t>
+          <t>2x45</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1x2x35 : 2x35</t>
+          <t>1x2x45 : 2x45</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>7349.7470703125</v>
+        <v>9036.947998046877</v>
       </c>
       <c r="F53" t="n">
-        <v>1435451</v>
+        <v>1840093</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>4.06396484375</v>
+        <v>6.433837890625</v>
       </c>
       <c r="I53" t="n">
-        <v>1475616</v>
+        <v>1889362</v>
       </c>
       <c r="J53" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="K53" t="n">
-        <v>3102.48388671875</v>
+        <v>10058.42626953125</v>
       </c>
       <c r="L53" t="n">
-        <v>1444132</v>
+        <v>1856770</v>
       </c>
       <c r="M53" t="n">
-        <v>0.6</v>
+        <v>0.91</v>
       </c>
       <c r="N53" t="n">
-        <v>66748.61303710938</v>
+        <v>104905.7021484375</v>
       </c>
       <c r="O53" t="n">
-        <v>1493300</v>
+        <v>1890431</v>
       </c>
       <c r="P53" t="n">
-        <v>4.03</v>
+        <v>2.74</v>
       </c>
       <c r="Q53" t="n">
-        <v>24.1708984375</v>
+        <v>38.452880859375</v>
       </c>
       <c r="R53" t="n">
-        <v>1493300</v>
+        <v>1890431</v>
       </c>
       <c r="S53" t="n">
-        <v>4.03</v>
+        <v>2.74</v>
       </c>
       <c r="T53" t="n">
-        <v>144096.3352050781</v>
+        <v>240401.2668457031</v>
       </c>
       <c r="U53" t="n">
-        <v>1493300</v>
+        <v>1890431</v>
       </c>
       <c r="V53" t="n">
-        <v>4.03</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1x2x35</t>
+          <t>1x2x45</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2x35</t>
+          <t>2x45</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1x2x35 : 2x35</t>
+          <t>1x2x45 : 2x45</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>4550.002197265625</v>
+        <v>10161.15869140625</v>
       </c>
       <c r="F54" t="n">
-        <v>1438382</v>
+        <v>1843452</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>6.27490234375</v>
+        <v>7.19677734375</v>
       </c>
       <c r="I54" t="n">
-        <v>1466533</v>
+        <v>1893865</v>
       </c>
       <c r="J54" t="n">
-        <v>1.96</v>
+        <v>2.73</v>
       </c>
       <c r="K54" t="n">
-        <v>3113.62109375</v>
+        <v>8871.572021484375</v>
       </c>
       <c r="L54" t="n">
-        <v>1447244</v>
+        <v>1854780</v>
       </c>
       <c r="M54" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="N54" t="n">
-        <v>66776.22607421875</v>
+        <v>104245.921875</v>
       </c>
       <c r="O54" t="n">
-        <v>1477214</v>
+        <v>1895230</v>
       </c>
       <c r="P54" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="Q54" t="n">
-        <v>24.04296875</v>
+        <v>39.606689453125</v>
       </c>
       <c r="R54" t="n">
-        <v>1477214</v>
+        <v>1895230</v>
       </c>
       <c r="S54" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="T54" t="n">
-        <v>144275.4580078125</v>
+        <v>240154.9807128907</v>
       </c>
       <c r="U54" t="n">
-        <v>1477214</v>
+        <v>1895230</v>
       </c>
       <c r="V54" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1x2x35</t>
+          <t>1x2x45</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2x35</t>
+          <t>2x45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1x2x35 : 2x35</t>
+          <t>1x2x45 : 2x45</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>6708.124755859375</v>
+        <v>23118.60595703125</v>
       </c>
       <c r="F55" t="n">
-        <v>1437874</v>
+        <v>1834797</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>6.76220703125</v>
+        <v>6.7216796875</v>
       </c>
       <c r="I55" t="n">
-        <v>1481790</v>
+        <v>1876683</v>
       </c>
       <c r="J55" t="n">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="K55" t="n">
-        <v>3508.971435546875</v>
+        <v>7479.30517578125</v>
       </c>
       <c r="L55" t="n">
-        <v>1448965</v>
+        <v>1848658</v>
       </c>
       <c r="M55" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="N55" t="n">
-        <v>66640.31713867188</v>
+        <v>104550.0661621094</v>
       </c>
       <c r="O55" t="n">
-        <v>1484509</v>
+        <v>1872135</v>
       </c>
       <c r="P55" t="n">
-        <v>3.24</v>
+        <v>2.03</v>
       </c>
       <c r="Q55" t="n">
-        <v>25.26123046875</v>
+        <v>38.36181640625</v>
       </c>
       <c r="R55" t="n">
-        <v>1484509</v>
+        <v>1872135</v>
       </c>
       <c r="S55" t="n">
-        <v>3.24</v>
+        <v>2.03</v>
       </c>
       <c r="T55" t="n">
-        <v>144251.2121582031</v>
+        <v>240625.6577148437</v>
       </c>
       <c r="U55" t="n">
-        <v>1484509</v>
+        <v>1872135</v>
       </c>
       <c r="V55" t="n">
-        <v>3.24</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1x2x35</t>
+          <t>1x2x45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2x35</t>
+          <t>2x45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1x2x35 : 2x35</t>
+          <t>1x2x45 : 2x45</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>4789.14013671875</v>
+        <v>8149.406005859375</v>
       </c>
       <c r="F56" t="n">
-        <v>1430567</v>
+        <v>1842609</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>4.322998046875</v>
+        <v>7.934326171875</v>
       </c>
       <c r="I56" t="n">
-        <v>1463811</v>
+        <v>1875292</v>
       </c>
       <c r="J56" t="n">
-        <v>2.32</v>
+        <v>1.77</v>
       </c>
       <c r="K56" t="n">
-        <v>1888.14990234375</v>
+        <v>6122.878173828125</v>
       </c>
       <c r="L56" t="n">
-        <v>1444297</v>
+        <v>1856664</v>
       </c>
       <c r="M56" t="n">
-        <v>0.96</v>
+        <v>0.76</v>
       </c>
       <c r="N56" t="n">
-        <v>66750.39599609375</v>
+        <v>104193.8342285156</v>
       </c>
       <c r="O56" t="n">
-        <v>1474210</v>
+        <v>1884846</v>
       </c>
       <c r="P56" t="n">
-        <v>3.05</v>
+        <v>2.29</v>
       </c>
       <c r="Q56" t="n">
-        <v>25.22998046875</v>
+        <v>39.9697265625</v>
       </c>
       <c r="R56" t="n">
-        <v>1474210</v>
+        <v>1884846</v>
       </c>
       <c r="S56" t="n">
-        <v>3.05</v>
+        <v>2.29</v>
       </c>
       <c r="T56" t="n">
-        <v>144598.8469238281</v>
+        <v>240206.2219238281</v>
       </c>
       <c r="U56" t="n">
-        <v>1474210</v>
+        <v>1884846</v>
       </c>
       <c r="V56" t="n">
-        <v>3.05</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1x2x35</t>
+          <t>1x2x45</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2x35</t>
+          <t>2x45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1x2x35 : 2x35</t>
+          <t>1x2x45 : 2x45</t>
         </is>
       </c>
       <c r="D57" t="n">
         <v>6</v>
       </c>
       <c r="E57" t="n">
-        <v>4615.259033203125</v>
+        <v>22064.2998046875</v>
       </c>
       <c r="F57" t="n">
-        <v>1437936</v>
+        <v>1834850</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>6.464111328125</v>
+        <v>7.202880859375</v>
       </c>
       <c r="I57" t="n">
-        <v>1483253</v>
+        <v>1864442</v>
       </c>
       <c r="J57" t="n">
-        <v>3.15</v>
+        <v>1.61</v>
       </c>
       <c r="K57" t="n">
-        <v>2843.82275390625</v>
+        <v>4480.68701171875</v>
       </c>
       <c r="L57" t="n">
-        <v>1449041</v>
+        <v>1845291</v>
       </c>
       <c r="M57" t="n">
-        <v>0.77</v>
+        <v>0.57</v>
       </c>
       <c r="N57" t="n">
-        <v>66529.05908203125</v>
+        <v>104671.0942382812</v>
       </c>
       <c r="O57" t="n">
-        <v>1485445</v>
+        <v>1889142</v>
       </c>
       <c r="P57" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="Q57" t="n">
-        <v>24.25</v>
+        <v>39.5029296875</v>
       </c>
       <c r="R57" t="n">
-        <v>1485445</v>
+        <v>1889142</v>
       </c>
       <c r="S57" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="T57" t="n">
-        <v>143874.7529296875</v>
+        <v>239663.3186035156</v>
       </c>
       <c r="U57" t="n">
-        <v>1485445</v>
+        <v>1889142</v>
       </c>
       <c r="V57" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1x2x35</t>
+          <t>1x2x45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2x35</t>
+          <t>2x45</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1x2x35 : 2x35</t>
+          <t>1x2x45 : 2x45</t>
         </is>
       </c>
       <c r="D58" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>4362.65185546875</v>
+        <v>12025.453125</v>
       </c>
       <c r="F58" t="n">
-        <v>1433244</v>
+        <v>1835241</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>6.316162109375</v>
+        <v>6.502685546875</v>
       </c>
       <c r="I58" t="n">
-        <v>1477587</v>
+        <v>1870630</v>
       </c>
       <c r="J58" t="n">
-        <v>3.09</v>
+        <v>1.93</v>
       </c>
       <c r="K58" t="n">
-        <v>2790.6630859375</v>
+        <v>5085.25390625</v>
       </c>
       <c r="L58" t="n">
-        <v>1441459</v>
+        <v>1848776</v>
       </c>
       <c r="M58" t="n">
-        <v>0.57</v>
+        <v>0.74</v>
       </c>
       <c r="N58" t="n">
-        <v>66415.44091796875</v>
+        <v>103949.5390625</v>
       </c>
       <c r="O58" t="n">
-        <v>1481356</v>
+        <v>1881803</v>
       </c>
       <c r="P58" t="n">
-        <v>3.36</v>
+        <v>2.54</v>
       </c>
       <c r="Q58" t="n">
-        <v>24.603271484375</v>
+        <v>39.079833984375</v>
       </c>
       <c r="R58" t="n">
-        <v>1481356</v>
+        <v>1881803</v>
       </c>
       <c r="S58" t="n">
-        <v>3.36</v>
+        <v>2.54</v>
       </c>
       <c r="T58" t="n">
-        <v>145033.4443359375</v>
+        <v>241563.0029296875</v>
       </c>
       <c r="U58" t="n">
-        <v>1481356</v>
+        <v>1881803</v>
       </c>
       <c r="V58" t="n">
-        <v>3.36</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1x2x35</t>
+          <t>1x2x45</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2x35</t>
+          <t>2x45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1x2x35 : 2x35</t>
+          <t>1x2x45 : 2x45</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>8</v>
       </c>
       <c r="E59" t="n">
-        <v>24869.9677734375</v>
+        <v>16908.37866210938</v>
       </c>
       <c r="F59" t="n">
-        <v>1443988</v>
+        <v>1844624</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>7.385498046875</v>
+        <v>6.461181640625</v>
       </c>
       <c r="I59" t="n">
-        <v>1489394</v>
+        <v>1892366</v>
       </c>
       <c r="J59" t="n">
-        <v>3.14</v>
+        <v>2.59</v>
       </c>
       <c r="K59" t="n">
-        <v>2702.533203125</v>
+        <v>5848.653076171875</v>
       </c>
       <c r="L59" t="n">
-        <v>1458879</v>
+        <v>1860769</v>
       </c>
       <c r="M59" t="n">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
       <c r="N59" t="n">
-        <v>66700.76293945312</v>
+        <v>104717.1369628906</v>
       </c>
       <c r="O59" t="n">
-        <v>1492860</v>
+        <v>1901089</v>
       </c>
       <c r="P59" t="n">
-        <v>3.38</v>
+        <v>3.06</v>
       </c>
       <c r="Q59" t="n">
-        <v>24.181884765625</v>
+        <v>39.57177734375</v>
       </c>
       <c r="R59" t="n">
-        <v>1492860</v>
+        <v>1901089</v>
       </c>
       <c r="S59" t="n">
-        <v>3.38</v>
+        <v>3.06</v>
       </c>
       <c r="T59" t="n">
-        <v>145358.6850585938</v>
+        <v>243138.447265625</v>
       </c>
       <c r="U59" t="n">
-        <v>1492860</v>
+        <v>1901089</v>
       </c>
       <c r="V59" t="n">
-        <v>3.38</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1x2x35</t>
+          <t>1x2x45</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2x35</t>
+          <t>2x45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1x2x35 : 2x35</t>
+          <t>1x2x45 : 2x45</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>9</v>
       </c>
       <c r="E60" t="n">
-        <v>4160.4931640625</v>
+        <v>12767.5283203125</v>
       </c>
       <c r="F60" t="n">
-        <v>1438503</v>
+        <v>1839962</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>4.069091796875</v>
+        <v>7.414794921875</v>
       </c>
       <c r="I60" t="n">
-        <v>1470984</v>
+        <v>1901727</v>
       </c>
       <c r="J60" t="n">
-        <v>2.26</v>
+        <v>3.36</v>
       </c>
       <c r="K60" t="n">
-        <v>1892.435791015625</v>
+        <v>6991.81396484375</v>
       </c>
       <c r="L60" t="n">
-        <v>1448328</v>
+        <v>1854619</v>
       </c>
       <c r="M60" t="n">
-        <v>0.68</v>
+        <v>0.8</v>
       </c>
       <c r="N60" t="n">
-        <v>66735.75610351562</v>
+        <v>105392.1430664062</v>
       </c>
       <c r="O60" t="n">
-        <v>1484528</v>
+        <v>1883748</v>
       </c>
       <c r="P60" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q60" t="n">
-        <v>24.6728515625</v>
+        <v>38.95703125</v>
       </c>
       <c r="R60" t="n">
-        <v>1484528</v>
+        <v>1883748</v>
       </c>
       <c r="S60" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="T60" t="n">
-        <v>144457.4851074219</v>
+        <v>241795.580078125</v>
       </c>
       <c r="U60" t="n">
-        <v>1484528</v>
+        <v>1883748</v>
       </c>
       <c r="V60" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1x2x35</t>
+          <t>1x2x45</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2x35</t>
+          <t>2x45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1x2x35 : 2x35</t>
+          <t>1x2x45 : 2x45</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>7</v>
       </c>
       <c r="E61" t="n">
-        <v>4023.376953125</v>
+        <v>18171.29614257812</v>
       </c>
       <c r="F61" t="n">
-        <v>1440524</v>
+        <v>1850376</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>5.260009765625</v>
+        <v>8.936767578125</v>
       </c>
       <c r="I61" t="n">
-        <v>1476434</v>
+        <v>1897577</v>
       </c>
       <c r="J61" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="K61" t="n">
-        <v>1890.6728515625</v>
+        <v>9193.56689453125</v>
       </c>
       <c r="L61" t="n">
-        <v>1455139</v>
+        <v>1862467</v>
       </c>
       <c r="M61" t="n">
-        <v>1.01</v>
+        <v>0.65</v>
       </c>
       <c r="N61" t="n">
-        <v>66941.5478515625</v>
+        <v>104196.3291015625</v>
       </c>
       <c r="O61" t="n">
-        <v>1486718</v>
+        <v>1913242</v>
       </c>
       <c r="P61" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="Q61" t="n">
-        <v>24.319091796875</v>
+        <v>40.10791015625</v>
       </c>
       <c r="R61" t="n">
-        <v>1486718</v>
+        <v>1913242</v>
       </c>
       <c r="S61" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="T61" t="n">
-        <v>144883.4907226562</v>
+        <v>239113.4672851562</v>
       </c>
       <c r="U61" t="n">
-        <v>1486718</v>
+        <v>1913242</v>
       </c>
       <c r="V61" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1x2x25</t>
+          <t>1x2x35</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2x25</t>
+          <t>2x35</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x25</t>
+          <t>1x2x35 : 2x35</t>
         </is>
       </c>
       <c r="D62" t="n">
         <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>1652.0400390625</v>
+        <v>8759.420166015625</v>
       </c>
       <c r="F62" t="n">
-        <v>1040409</v>
+        <v>1441753</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>2.294189453125</v>
+        <v>5.830810546875</v>
       </c>
       <c r="I62" t="n">
-        <v>1085730</v>
+        <v>1483243</v>
       </c>
       <c r="J62" t="n">
-        <v>4.36</v>
+        <v>2.88</v>
       </c>
       <c r="K62" t="n">
-        <v>894.791015625</v>
+        <v>2092.8388671875</v>
       </c>
       <c r="L62" t="n">
-        <v>1046565</v>
+        <v>1452833</v>
       </c>
       <c r="M62" t="n">
-        <v>0.59</v>
+        <v>0.77</v>
       </c>
       <c r="N62" t="n">
-        <v>36101.8779296875</v>
+        <v>66502.51708984375</v>
       </c>
       <c r="O62" t="n">
-        <v>1070758</v>
+        <v>1491193</v>
       </c>
       <c r="P62" t="n">
-        <v>2.92</v>
+        <v>3.43</v>
       </c>
       <c r="Q62" t="n">
-        <v>13.473876953125</v>
+        <v>24.9599609375</v>
       </c>
       <c r="R62" t="n">
-        <v>1070758</v>
+        <v>1491193</v>
       </c>
       <c r="S62" t="n">
-        <v>2.92</v>
+        <v>3.43</v>
       </c>
       <c r="T62" t="n">
-        <v>73812.14892578125</v>
+        <v>144426.9968261719</v>
       </c>
       <c r="U62" t="n">
-        <v>1070758</v>
+        <v>1491193</v>
       </c>
       <c r="V62" t="n">
-        <v>2.92</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1x2x25</t>
+          <t>1x2x35</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2x25</t>
+          <t>2x35</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x25</t>
+          <t>1x2x35 : 2x35</t>
         </is>
       </c>
       <c r="D63" t="n">
         <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>3266.573974609375</v>
+        <v>7349.7470703125</v>
       </c>
       <c r="F63" t="n">
-        <v>1044804</v>
+        <v>1435451</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>2.227294921875</v>
+        <v>4.06396484375</v>
       </c>
       <c r="I63" t="n">
-        <v>1088017</v>
+        <v>1475616</v>
       </c>
       <c r="J63" t="n">
-        <v>4.14</v>
+        <v>2.8</v>
       </c>
       <c r="K63" t="n">
-        <v>1305.9111328125</v>
+        <v>3102.48388671875</v>
       </c>
       <c r="L63" t="n">
-        <v>1051058</v>
+        <v>1444132</v>
       </c>
       <c r="M63" t="n">
         <v>0.6</v>
       </c>
       <c r="N63" t="n">
-        <v>36697.07885742188</v>
+        <v>66748.61303710938</v>
       </c>
       <c r="O63" t="n">
-        <v>1103579</v>
+        <v>1493300</v>
       </c>
       <c r="P63" t="n">
-        <v>5.63</v>
+        <v>4.03</v>
       </c>
       <c r="Q63" t="n">
-        <v>13.675048828125</v>
+        <v>24.1708984375</v>
       </c>
       <c r="R63" t="n">
-        <v>1103579</v>
+        <v>1493300</v>
       </c>
       <c r="S63" t="n">
-        <v>5.63</v>
+        <v>4.03</v>
       </c>
       <c r="T63" t="n">
-        <v>73222.36889648438</v>
+        <v>144096.3352050781</v>
       </c>
       <c r="U63" t="n">
-        <v>1103579</v>
+        <v>1493300</v>
       </c>
       <c r="V63" t="n">
-        <v>5.63</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1x2x25</t>
+          <t>1x2x35</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2x25</t>
+          <t>2x35</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x25</t>
+          <t>1x2x35 : 2x35</t>
         </is>
       </c>
       <c r="D64" t="n">
         <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>1662.120361328125</v>
+        <v>4550.002197265625</v>
       </c>
       <c r="F64" t="n">
-        <v>1039657</v>
+        <v>1438382</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>2.32421875</v>
+        <v>6.27490234375</v>
       </c>
       <c r="I64" t="n">
-        <v>1062180</v>
+        <v>1466533</v>
       </c>
       <c r="J64" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="K64" t="n">
-        <v>578.37109375</v>
+        <v>3113.62109375</v>
       </c>
       <c r="L64" t="n">
-        <v>1049421</v>
+        <v>1447244</v>
       </c>
       <c r="M64" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="N64" t="n">
-        <v>36209.08081054688</v>
+        <v>66776.22607421875</v>
       </c>
       <c r="O64" t="n">
-        <v>1076398</v>
+        <v>1477214</v>
       </c>
       <c r="P64" t="n">
-        <v>3.53</v>
+        <v>2.7</v>
       </c>
       <c r="Q64" t="n">
-        <v>13.903076171875</v>
+        <v>24.04296875</v>
       </c>
       <c r="R64" t="n">
-        <v>1076398</v>
+        <v>1477214</v>
       </c>
       <c r="S64" t="n">
-        <v>3.53</v>
+        <v>2.7</v>
       </c>
       <c r="T64" t="n">
-        <v>73434.31909179688</v>
+        <v>144275.4580078125</v>
       </c>
       <c r="U64" t="n">
-        <v>1076398</v>
+        <v>1477214</v>
       </c>
       <c r="V64" t="n">
-        <v>3.53</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1x2x25</t>
+          <t>1x2x35</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2x25</t>
+          <t>2x35</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x25</t>
+          <t>1x2x35 : 2x35</t>
         </is>
       </c>
       <c r="D65" t="n">
         <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>1701.872802734375</v>
+        <v>6708.124755859375</v>
       </c>
       <c r="F65" t="n">
-        <v>1045875</v>
+        <v>1437874</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>2.30322265625</v>
+        <v>6.76220703125</v>
       </c>
       <c r="I65" t="n">
-        <v>1064087</v>
+        <v>1481790</v>
       </c>
       <c r="J65" t="n">
-        <v>1.74</v>
+        <v>3.05</v>
       </c>
       <c r="K65" t="n">
-        <v>313.4111328125</v>
+        <v>3508.971435546875</v>
       </c>
       <c r="L65" t="n">
-        <v>1054835</v>
+        <v>1448965</v>
       </c>
       <c r="M65" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="N65" t="n">
-        <v>36070.98828125</v>
+        <v>66640.31713867188</v>
       </c>
       <c r="O65" t="n">
-        <v>1071871</v>
+        <v>1484509</v>
       </c>
       <c r="P65" t="n">
-        <v>2.49</v>
+        <v>3.24</v>
       </c>
       <c r="Q65" t="n">
-        <v>13.503173828125</v>
+        <v>25.26123046875</v>
       </c>
       <c r="R65" t="n">
-        <v>1071871</v>
+        <v>1484509</v>
       </c>
       <c r="S65" t="n">
-        <v>2.49</v>
+        <v>3.24</v>
       </c>
       <c r="T65" t="n">
-        <v>73356.39892578125</v>
+        <v>144251.2121582031</v>
       </c>
       <c r="U65" t="n">
-        <v>1071871</v>
+        <v>1484509</v>
       </c>
       <c r="V65" t="n">
-        <v>2.49</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1x2x25</t>
+          <t>1x2x35</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2x25</t>
+          <t>2x35</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x25</t>
+          <t>1x2x35 : 2x35</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>10</v>
       </c>
       <c r="E66" t="n">
-        <v>2543.71484375</v>
+        <v>4789.14013671875</v>
       </c>
       <c r="F66" t="n">
-        <v>1037475</v>
+        <v>1430567</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>2.222900390625</v>
+        <v>4.322998046875</v>
       </c>
       <c r="I66" t="n">
-        <v>1082506</v>
+        <v>1463811</v>
       </c>
       <c r="J66" t="n">
-        <v>4.34</v>
+        <v>2.32</v>
       </c>
       <c r="K66" t="n">
-        <v>1311.80126953125</v>
+        <v>1888.14990234375</v>
       </c>
       <c r="L66" t="n">
-        <v>1045215</v>
+        <v>1444297</v>
       </c>
       <c r="M66" t="n">
-        <v>0.75</v>
+        <v>0.96</v>
       </c>
       <c r="N66" t="n">
-        <v>36254.85400390625</v>
+        <v>66750.39599609375</v>
       </c>
       <c r="O66" t="n">
-        <v>1076324</v>
+        <v>1474210</v>
       </c>
       <c r="P66" t="n">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="Q66" t="n">
-        <v>13.97509765625</v>
+        <v>25.22998046875</v>
       </c>
       <c r="R66" t="n">
-        <v>1076324</v>
+        <v>1474210</v>
       </c>
       <c r="S66" t="n">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="T66" t="n">
-        <v>73197.71411132812</v>
+        <v>144598.8469238281</v>
       </c>
       <c r="U66" t="n">
-        <v>1076324</v>
+        <v>1474210</v>
       </c>
       <c r="V66" t="n">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1x2x25</t>
+          <t>1x2x35</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2x25</t>
+          <t>2x35</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x25</t>
+          <t>1x2x35 : 2x35</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>2862.10009765625</v>
+        <v>4615.259033203125</v>
       </c>
       <c r="F67" t="n">
-        <v>1046192</v>
+        <v>1437936</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>2.239990234375</v>
+        <v>6.464111328125</v>
       </c>
       <c r="I67" t="n">
-        <v>1091082</v>
+        <v>1483253</v>
       </c>
       <c r="J67" t="n">
-        <v>4.29</v>
+        <v>3.15</v>
       </c>
       <c r="K67" t="n">
-        <v>795.558837890625</v>
+        <v>2843.82275390625</v>
       </c>
       <c r="L67" t="n">
-        <v>1057231</v>
+        <v>1449041</v>
       </c>
       <c r="M67" t="n">
-        <v>1.06</v>
+        <v>0.77</v>
       </c>
       <c r="N67" t="n">
-        <v>36381.35302734375</v>
+        <v>66529.05908203125</v>
       </c>
       <c r="O67" t="n">
-        <v>1089394</v>
+        <v>1485445</v>
       </c>
       <c r="P67" t="n">
-        <v>4.13</v>
+        <v>3.3</v>
       </c>
       <c r="Q67" t="n">
-        <v>13.80078125</v>
+        <v>24.25</v>
       </c>
       <c r="R67" t="n">
-        <v>1089394</v>
+        <v>1485445</v>
       </c>
       <c r="S67" t="n">
-        <v>4.13</v>
+        <v>3.3</v>
       </c>
       <c r="T67" t="n">
-        <v>73001.14624023438</v>
+        <v>143874.7529296875</v>
       </c>
       <c r="U67" t="n">
-        <v>1089394</v>
+        <v>1485445</v>
       </c>
       <c r="V67" t="n">
-        <v>4.13</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1x2x25</t>
+          <t>1x2x35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2x25</t>
+          <t>2x35</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x25</t>
+          <t>1x2x35 : 2x35</t>
         </is>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1876.322998046875</v>
+        <v>4362.65185546875</v>
       </c>
       <c r="F68" t="n">
-        <v>1038964</v>
+        <v>1433244</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>2.240966796875</v>
+        <v>6.316162109375</v>
       </c>
       <c r="I68" t="n">
-        <v>1078076</v>
+        <v>1477587</v>
       </c>
       <c r="J68" t="n">
-        <v>3.76</v>
+        <v>3.09</v>
       </c>
       <c r="K68" t="n">
-        <v>1025.31982421875</v>
+        <v>2790.6630859375</v>
       </c>
       <c r="L68" t="n">
-        <v>1050631</v>
+        <v>1441459</v>
       </c>
       <c r="M68" t="n">
-        <v>1.12</v>
+        <v>0.57</v>
       </c>
       <c r="N68" t="n">
-        <v>36197.171875</v>
+        <v>66415.44091796875</v>
       </c>
       <c r="O68" t="n">
-        <v>1071930</v>
+        <v>1481356</v>
       </c>
       <c r="P68" t="n">
-        <v>3.17</v>
+        <v>3.36</v>
       </c>
       <c r="Q68" t="n">
-        <v>13.457275390625</v>
+        <v>24.603271484375</v>
       </c>
       <c r="R68" t="n">
-        <v>1071930</v>
+        <v>1481356</v>
       </c>
       <c r="S68" t="n">
-        <v>3.17</v>
+        <v>3.36</v>
       </c>
       <c r="T68" t="n">
-        <v>73742.33813476562</v>
+        <v>145033.4443359375</v>
       </c>
       <c r="U68" t="n">
-        <v>1071930</v>
+        <v>1481356</v>
       </c>
       <c r="V68" t="n">
-        <v>3.17</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1x2x25</t>
+          <t>1x2x35</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2x25</t>
+          <t>2x35</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x25</t>
+          <t>1x2x35 : 2x35</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>8</v>
       </c>
       <c r="E69" t="n">
-        <v>3602.097900390625</v>
+        <v>24869.9677734375</v>
       </c>
       <c r="F69" t="n">
-        <v>1037849</v>
+        <v>1443988</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>2.2421875</v>
+        <v>7.385498046875</v>
       </c>
       <c r="I69" t="n">
-        <v>1071731</v>
+        <v>1489394</v>
       </c>
       <c r="J69" t="n">
-        <v>3.26</v>
+        <v>3.14</v>
       </c>
       <c r="K69" t="n">
-        <v>895.288330078125</v>
+        <v>2702.533203125</v>
       </c>
       <c r="L69" t="n">
-        <v>1046703</v>
+        <v>1458879</v>
       </c>
       <c r="M69" t="n">
-        <v>0.85</v>
+        <v>1.03</v>
       </c>
       <c r="N69" t="n">
-        <v>36181.40600585938</v>
+        <v>66700.76293945312</v>
       </c>
       <c r="O69" t="n">
-        <v>1077650</v>
+        <v>1492860</v>
       </c>
       <c r="P69" t="n">
-        <v>3.83</v>
+        <v>3.38</v>
       </c>
       <c r="Q69" t="n">
-        <v>13.837890625</v>
+        <v>24.181884765625</v>
       </c>
       <c r="R69" t="n">
-        <v>1077650</v>
+        <v>1492860</v>
       </c>
       <c r="S69" t="n">
-        <v>3.83</v>
+        <v>3.38</v>
       </c>
       <c r="T69" t="n">
-        <v>73286.470703125</v>
+        <v>145358.6850585938</v>
       </c>
       <c r="U69" t="n">
-        <v>1077650</v>
+        <v>1492860</v>
       </c>
       <c r="V69" t="n">
-        <v>3.83</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1x2x25</t>
+          <t>1x2x35</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2x25</t>
+          <t>2x35</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x25</t>
+          <t>1x2x35 : 2x35</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>9</v>
       </c>
       <c r="E70" t="n">
-        <v>1496.052978515625</v>
+        <v>4160.4931640625</v>
       </c>
       <c r="F70" t="n">
-        <v>1040933</v>
+        <v>1438503</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>2.204833984375</v>
+        <v>4.069091796875</v>
       </c>
       <c r="I70" t="n">
-        <v>1071210</v>
+        <v>1470984</v>
       </c>
       <c r="J70" t="n">
-        <v>2.91</v>
+        <v>2.26</v>
       </c>
       <c r="K70" t="n">
-        <v>1053.93505859375</v>
+        <v>1892.435791015625</v>
       </c>
       <c r="L70" t="n">
-        <v>1051982</v>
+        <v>1448328</v>
       </c>
       <c r="M70" t="n">
-        <v>1.06</v>
+        <v>0.68</v>
       </c>
       <c r="N70" t="n">
-        <v>36409.65502929688</v>
+        <v>66735.75610351562</v>
       </c>
       <c r="O70" t="n">
-        <v>1071992</v>
+        <v>1484528</v>
       </c>
       <c r="P70" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="Q70" t="n">
-        <v>13.93603515625</v>
+        <v>24.6728515625</v>
       </c>
       <c r="R70" t="n">
-        <v>1071992</v>
+        <v>1484528</v>
       </c>
       <c r="S70" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="T70" t="n">
-        <v>73437.05102539062</v>
+        <v>144457.4851074219</v>
       </c>
       <c r="U70" t="n">
-        <v>1071992</v>
+        <v>1484528</v>
       </c>
       <c r="V70" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1x2x25</t>
+          <t>1x2x35</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2x25</t>
+          <t>2x35</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x25</t>
+          <t>1x2x35 : 2x35</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>7</v>
       </c>
       <c r="E71" t="n">
-        <v>4065.589111328125</v>
+        <v>4023.376953125</v>
       </c>
       <c r="F71" t="n">
-        <v>1035898</v>
+        <v>1440524</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>2.23095703125</v>
+        <v>5.260009765625</v>
       </c>
       <c r="I71" t="n">
-        <v>1067971</v>
+        <v>1476434</v>
       </c>
       <c r="J71" t="n">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="K71" t="n">
-        <v>948.492919921875</v>
+        <v>1890.6728515625</v>
       </c>
       <c r="L71" t="n">
-        <v>1041776</v>
+        <v>1455139</v>
       </c>
       <c r="M71" t="n">
-        <v>0.57</v>
+        <v>1.01</v>
       </c>
       <c r="N71" t="n">
-        <v>36543.14794921875</v>
+        <v>66941.5478515625</v>
       </c>
       <c r="O71" t="n">
-        <v>1073112</v>
+        <v>1486718</v>
       </c>
       <c r="P71" t="n">
-        <v>3.59</v>
+        <v>3.21</v>
       </c>
       <c r="Q71" t="n">
-        <v>14.2470703125</v>
+        <v>24.319091796875</v>
       </c>
       <c r="R71" t="n">
-        <v>1073112</v>
+        <v>1486718</v>
       </c>
       <c r="S71" t="n">
-        <v>3.59</v>
+        <v>3.21</v>
       </c>
       <c r="T71" t="n">
-        <v>73405.91284179688</v>
+        <v>144883.4907226562</v>
       </c>
       <c r="U71" t="n">
-        <v>1073112</v>
+        <v>1486718</v>
       </c>
       <c r="V71" t="n">
-        <v>3.59</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="72">
@@ -5728,41 +5728,71 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2x40</t>
+          <t>2x25</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x40</t>
+          <t>1x2x25 : 2x25</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2132.921875</v>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+        <v>1652.0400390625</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1040409</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2.294189453125</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1085730</v>
+      </c>
+      <c r="J72" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="K72" t="n">
+        <v>894.791015625</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1046565</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.59</v>
+      </c>
       <c r="N72" t="n">
-        <v>51136.3779296875</v>
+        <v>36101.8779296875</v>
       </c>
       <c r="O72" t="n">
-        <v>1035806</v>
-      </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
+        <v>1070758</v>
+      </c>
+      <c r="P72" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>13.473876953125</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1070758</v>
+      </c>
+      <c r="S72" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T72" t="n">
+        <v>73812.14892578125</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1070758</v>
+      </c>
+      <c r="V72" t="n">
+        <v>2.92</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5772,41 +5802,71 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2x40</t>
+          <t>2x25</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x40</t>
+          <t>1x2x25 : 2x25</t>
         </is>
       </c>
       <c r="D73" t="n">
         <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>2165.9970703125</v>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+        <v>3266.573974609375</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1044804</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2.227294921875</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1088017</v>
+      </c>
+      <c r="J73" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1305.9111328125</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1051058</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.6</v>
+      </c>
       <c r="N73" t="n">
-        <v>51188.80297851562</v>
+        <v>36697.07885742188</v>
       </c>
       <c r="O73" t="n">
-        <v>1039680</v>
-      </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
+        <v>1103579</v>
+      </c>
+      <c r="P73" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>13.675048828125</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1103579</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="T73" t="n">
+        <v>73222.36889648438</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1103579</v>
+      </c>
+      <c r="V73" t="n">
+        <v>5.63</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5816,41 +5876,71 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2x40</t>
+          <t>2x25</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x40</t>
+          <t>1x2x25 : 2x25</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>4</v>
       </c>
       <c r="E74" t="n">
-        <v>2138.51171875</v>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+        <v>1662.120361328125</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1039657</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2.32421875</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1062180</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K74" t="n">
+        <v>578.37109375</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1049421</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="N74" t="n">
-        <v>51346.24682617188</v>
+        <v>36209.08081054688</v>
       </c>
       <c r="O74" t="n">
-        <v>1031502</v>
-      </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
+        <v>1076398</v>
+      </c>
+      <c r="P74" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>13.903076171875</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1076398</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="T74" t="n">
+        <v>73434.31909179688</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1076398</v>
+      </c>
+      <c r="V74" t="n">
+        <v>3.53</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5860,41 +5950,71 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2x40</t>
+          <t>2x25</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x40</t>
+          <t>1x2x25 : 2x25</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>2174.744873046875</v>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+        <v>1701.872802734375</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1045875</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2.30322265625</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1064087</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="K75" t="n">
+        <v>313.4111328125</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1054835</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.86</v>
+      </c>
       <c r="N75" t="n">
-        <v>50910.91625976562</v>
+        <v>36070.98828125</v>
       </c>
       <c r="O75" t="n">
-        <v>1049632</v>
-      </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
+        <v>1071871</v>
+      </c>
+      <c r="P75" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>13.503173828125</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1071871</v>
+      </c>
+      <c r="S75" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T75" t="n">
+        <v>73356.39892578125</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1071871</v>
+      </c>
+      <c r="V75" t="n">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5904,41 +6024,71 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2x40</t>
+          <t>2x25</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x40</t>
+          <t>1x2x25 : 2x25</t>
         </is>
       </c>
       <c r="D76" t="n">
         <v>10</v>
       </c>
       <c r="E76" t="n">
-        <v>2155.519287109375</v>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+        <v>2543.71484375</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1037475</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2.222900390625</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1082506</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1311.80126953125</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1045215</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.75</v>
+      </c>
       <c r="N76" t="n">
-        <v>51038.76806640625</v>
+        <v>36254.85400390625</v>
       </c>
       <c r="O76" t="n">
-        <v>1053652</v>
-      </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
+        <v>1076324</v>
+      </c>
+      <c r="P76" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>13.97509765625</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1076324</v>
+      </c>
+      <c r="S76" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="T76" t="n">
+        <v>73197.71411132812</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1076324</v>
+      </c>
+      <c r="V76" t="n">
+        <v>3.74</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5948,41 +6098,71 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2x40</t>
+          <t>2x25</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x40</t>
+          <t>1x2x25 : 2x25</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>6</v>
       </c>
       <c r="E77" t="n">
-        <v>2144.879638671875</v>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
+        <v>2862.10009765625</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1046192</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2.239990234375</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1091082</v>
+      </c>
+      <c r="J77" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="K77" t="n">
+        <v>795.558837890625</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1057231</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.06</v>
+      </c>
       <c r="N77" t="n">
-        <v>51119.50805664063</v>
+        <v>36381.35302734375</v>
       </c>
       <c r="O77" t="n">
-        <v>1044543</v>
-      </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
+        <v>1089394</v>
+      </c>
+      <c r="P77" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>13.80078125</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1089394</v>
+      </c>
+      <c r="S77" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="T77" t="n">
+        <v>73001.14624023438</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1089394</v>
+      </c>
+      <c r="V77" t="n">
+        <v>4.13</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5992,41 +6172,71 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2x40</t>
+          <t>2x25</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x40</t>
+          <t>1x2x25 : 2x25</t>
         </is>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>2179.531982421875</v>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
+        <v>1876.322998046875</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1038964</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2.240966796875</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1078076</v>
+      </c>
+      <c r="J78" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1025.31982421875</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1050631</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.12</v>
+      </c>
       <c r="N78" t="n">
-        <v>51302.98510742188</v>
+        <v>36197.171875</v>
       </c>
       <c r="O78" t="n">
-        <v>1038693</v>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
+        <v>1071930</v>
+      </c>
+      <c r="P78" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>13.457275390625</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1071930</v>
+      </c>
+      <c r="S78" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="T78" t="n">
+        <v>73742.33813476562</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1071930</v>
+      </c>
+      <c r="V78" t="n">
+        <v>3.17</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6036,41 +6246,71 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2x40</t>
+          <t>2x25</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x40</t>
+          <t>1x2x25 : 2x25</t>
         </is>
       </c>
       <c r="D79" t="n">
         <v>8</v>
       </c>
       <c r="E79" t="n">
-        <v>2170.497802734375</v>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
+        <v>3602.097900390625</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1037849</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2.2421875</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1071731</v>
+      </c>
+      <c r="J79" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="K79" t="n">
+        <v>895.288330078125</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1046703</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.85</v>
+      </c>
       <c r="N79" t="n">
-        <v>51116.10278320312</v>
+        <v>36181.40600585938</v>
       </c>
       <c r="O79" t="n">
-        <v>1037232</v>
-      </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
+        <v>1077650</v>
+      </c>
+      <c r="P79" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>13.837890625</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1077650</v>
+      </c>
+      <c r="S79" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="T79" t="n">
+        <v>73286.470703125</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1077650</v>
+      </c>
+      <c r="V79" t="n">
+        <v>3.83</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6080,41 +6320,71 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2x40</t>
+          <t>2x25</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x40</t>
+          <t>1x2x25 : 2x25</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>9</v>
       </c>
       <c r="E80" t="n">
-        <v>2135.47607421875</v>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
+        <v>1496.052978515625</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1040933</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2.204833984375</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1071210</v>
+      </c>
+      <c r="J80" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1053.93505859375</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1051982</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.06</v>
+      </c>
       <c r="N80" t="n">
-        <v>51088.56494140625</v>
+        <v>36409.65502929688</v>
       </c>
       <c r="O80" t="n">
-        <v>1044623</v>
-      </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
+        <v>1071992</v>
+      </c>
+      <c r="P80" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>13.93603515625</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1071992</v>
+      </c>
+      <c r="S80" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T80" t="n">
+        <v>73437.05102539062</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1071992</v>
+      </c>
+      <c r="V80" t="n">
+        <v>2.98</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6124,41 +6394,71 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2x40</t>
+          <t>2x25</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1x2x25 : 2x40</t>
+          <t>1x2x25 : 2x25</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>7</v>
       </c>
       <c r="E81" t="n">
-        <v>2137.094970703125</v>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
+        <v>4065.589111328125</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1035898</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2.23095703125</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1067971</v>
+      </c>
+      <c r="J81" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>948.492919921875</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1041776</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.57</v>
+      </c>
       <c r="N81" t="n">
-        <v>50972.59399414063</v>
+        <v>36543.14794921875</v>
       </c>
       <c r="O81" t="n">
-        <v>1033928</v>
-      </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
+        <v>1073112</v>
+      </c>
+      <c r="P81" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>14.2470703125</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1073112</v>
+      </c>
+      <c r="S81" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="T81" t="n">
+        <v>73405.91284179688</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1073112</v>
+      </c>
+      <c r="V81" t="n">
+        <v>3.59</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
